--- a/volunteersync/test/e2e/reports/appium_e2e_report.xlsx
+++ b/volunteersync/test/e2e/reports/appium_e2e_report.xlsx
@@ -20,7 +20,7 @@
     <t>Generated At</t>
   </si>
   <si>
-    <t>23/7/2026, 10:21:23 am</t>
+    <t>25/7/2026, 9:30:25 pm</t>
   </si>
   <si>
     <t>Suite</t>
@@ -142,7 +142,7 @@
     <t>Landing screen renders with hero text "VolunteerSync"</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:00.685Z</t>
+    <t>2026-07-25T16:00:09.568Z</t>
   </si>
   <si>
     <t>Mocked execution – no real device required</t>
@@ -165,7 +165,7 @@
     <t>"Get Started" button is visible and clickable</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:00.749Z</t>
+    <t>2026-07-25T16:00:09.615Z</t>
   </si>
   <si>
     <t>LND-APP-03</t>
@@ -184,7 +184,7 @@
     <t>VolunteerSync logo/brand is displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:00.773Z</t>
+    <t>2026-07-25T16:00:09.646Z</t>
   </si>
   <si>
     <t>LND-APP-04</t>
@@ -201,7 +201,7 @@
     <t>Login screen loads with email and password fields</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:00.798Z</t>
+    <t>2026-07-25T16:00:09.676Z</t>
   </si>
   <si>
     <t>LND-APP-05</t>
@@ -218,7 +218,7 @@
     <t>Feature cards render correctly when scrolled</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:00.823Z</t>
+    <t>2026-07-25T16:00:09.706Z</t>
   </si>
   <si>
     <t>LND-APP-06</t>
@@ -237,7 +237,7 @@
     <t>Footer with copyright text is displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:00.903Z</t>
+    <t>2026-07-25T16:00:09.737Z</t>
   </si>
   <si>
     <t>LND-APP-07</t>
@@ -257,7 +257,7 @@
     <t>Tagline reads "Empowering Volunteers, Building Communities"</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:00.943Z</t>
+    <t>2026-07-25T16:00:09.768Z</t>
   </si>
   <si>
     <t>LND-APP-08</t>
@@ -274,7 +274,7 @@
     <t>Register form with name/email/password fields is visible</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:00.976Z</t>
+    <t>2026-07-25T16:00:09.799Z</t>
   </si>
   <si>
     <t>LND-APP-09</t>
@@ -291,7 +291,7 @@
     <t>Hero elements fade in without visual glitches</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.011Z</t>
+    <t>2026-07-25T16:00:09.829Z</t>
   </si>
   <si>
     <t>LND-APP-10</t>
@@ -307,7 +307,7 @@
     <t>Nav has: Home, Features, About, Get Started</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.032Z</t>
+    <t>2026-07-25T16:00:09.861Z</t>
   </si>
   <si>
     <t>LOG-APP-01</t>
@@ -323,7 +323,7 @@
     <t>All Login form elements are visible</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.062Z</t>
+    <t>2026-07-25T16:00:09.891Z</t>
   </si>
   <si>
     <t>LOG-APP-02</t>
@@ -343,7 +343,7 @@
     <t>Email and password validation errors are shown</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.090Z</t>
+    <t>2026-07-25T16:00:09.921Z</t>
   </si>
   <si>
     <t>LOG-APP-03</t>
@@ -360,7 +360,7 @@
     <t>"Enter a valid email address" error is shown</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.115Z</t>
+    <t>2026-07-25T16:00:09.951Z</t>
   </si>
   <si>
     <t>LOG-APP-04</t>
@@ -378,7 +378,7 @@
     <t>"Password must be at least 6 characters" error is shown</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.143Z</t>
+    <t>2026-07-25T16:00:09.982Z</t>
   </si>
   <si>
     <t>LOG-APP-05</t>
@@ -395,7 +395,7 @@
     <t>Forgot Password screen is displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.171Z</t>
+    <t>2026-07-25T16:00:10.051Z</t>
   </si>
   <si>
     <t>LOG-APP-06</t>
@@ -412,7 +412,7 @@
     <t>Register screen loads correctly</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.194Z</t>
+    <t>2026-07-25T16:00:10.091Z</t>
   </si>
   <si>
     <t>LOG-APP-07</t>
@@ -433,7 +433,7 @@
     <t>Password toggle shows/hides password characters</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.226Z</t>
+    <t>2026-07-25T16:00:10.121Z</t>
   </si>
   <si>
     <t>LOG-APP-08</t>
@@ -450,7 +450,7 @@
     <t>User is logged in and Dashboard loads</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.247Z</t>
+    <t>2026-07-25T16:00:10.152Z</t>
   </si>
   <si>
     <t>LOG-APP-09</t>
@@ -467,7 +467,7 @@
     <t>"Invalid credentials" snackbar is displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.275Z</t>
+    <t>2026-07-25T16:00:10.183Z</t>
   </si>
   <si>
     <t>LOG-APP-10</t>
@@ -483,7 +483,7 @@
     <t>Background gradient is visible and matches design</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.297Z</t>
+    <t>2026-07-25T16:00:10.214Z</t>
   </si>
   <si>
     <t>LOG-APP-11</t>
@@ -504,7 +504,7 @@
     <t>Keyboard opens and text is entered correctly</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.318Z</t>
+    <t>2026-07-25T16:00:10.246Z</t>
   </si>
   <si>
     <t>LOG-APP-12</t>
@@ -521,7 +521,7 @@
     <t>Focus moves to password field</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.351Z</t>
+    <t>2026-07-25T16:00:10.278Z</t>
   </si>
   <si>
     <t>REG-APP-01</t>
@@ -537,7 +537,7 @@
     <t>All registration fields are visible</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.379Z</t>
+    <t>2026-07-25T16:00:10.308Z</t>
   </si>
   <si>
     <t>REG-APP-02</t>
@@ -551,7 +551,7 @@
     <t>All required field validation errors are shown</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.407Z</t>
+    <t>2026-07-25T16:00:10.338Z</t>
   </si>
   <si>
     <t>REG-APP-03</t>
@@ -568,7 +568,7 @@
     <t>"Enter a valid email" error is shown</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.435Z</t>
+    <t>2026-07-25T16:00:10.370Z</t>
   </si>
   <si>
     <t>REG-APP-04</t>
@@ -586,7 +586,7 @@
     <t>"Passwords do not match" error is shown</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.469Z</t>
+    <t>2026-07-25T16:00:10.401Z</t>
   </si>
   <si>
     <t>REG-APP-05</t>
@@ -603,7 +603,7 @@
     <t>User account created and redirected to Dashboard</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.505Z</t>
+    <t>2026-07-25T16:00:10.431Z</t>
   </si>
   <si>
     <t>REG-APP-06</t>
@@ -619,7 +619,7 @@
     <t>Password strength indicator shows "Weak"</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.539Z</t>
+    <t>2026-07-25T16:00:10.461Z</t>
   </si>
   <si>
     <t>REG-APP-07</t>
@@ -636,7 +636,7 @@
     <t>Login screen is displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.573Z</t>
+    <t>2026-07-25T16:00:10.492Z</t>
   </si>
   <si>
     <t>REG-APP-08</t>
@@ -654,7 +654,7 @@
     <t>"Name is required" validation error appears</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.608Z</t>
+    <t>2026-07-25T16:00:10.523Z</t>
   </si>
   <si>
     <t>REG-APP-09</t>
@@ -671,7 +671,7 @@
     <t>Role dropdown opens and selection is saved</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.636Z</t>
+    <t>2026-07-25T16:00:10.554Z</t>
   </si>
   <si>
     <t>REG-APP-10</t>
@@ -688,7 +688,7 @@
     <t>Both password fields toggle visibility independently</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.664Z</t>
+    <t>2026-07-25T16:00:10.584Z</t>
   </si>
   <si>
     <t>FP-APP-01</t>
@@ -704,7 +704,7 @@
     <t>Forgot Password form is fully visible</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.694Z</t>
+    <t>2026-07-25T16:00:10.616Z</t>
   </si>
   <si>
     <t>FP-APP-02</t>
@@ -720,7 +720,7 @@
     <t>"Email is required" error is shown</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.718Z</t>
+    <t>2026-07-25T16:00:10.647Z</t>
   </si>
   <si>
     <t>FP-APP-03</t>
@@ -737,7 +737,7 @@
     <t>Success message "Password reset email sent" is shown</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.754Z</t>
+    <t>2026-07-25T16:00:10.678Z</t>
   </si>
   <si>
     <t>FP-APP-04</t>
@@ -754,7 +754,7 @@
     <t>User returns to Login screen</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.789Z</t>
+    <t>2026-07-25T16:00:10.709Z</t>
   </si>
   <si>
     <t>FP-APP-05</t>
@@ -765,7 +765,7 @@
 3. Assert error</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.825Z</t>
+    <t>2026-07-25T16:00:10.741Z</t>
   </si>
   <si>
     <t>DASH-APP-01</t>
@@ -782,7 +782,7 @@
     <t>Dashboard renders with title "Dashboard Overview"</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.858Z</t>
+    <t>2026-07-25T16:00:10.771Z</t>
   </si>
   <si>
     <t>Mocked execution</t>
@@ -801,7 +801,7 @@
     <t>Greeting "Good morning, [FirstName] 👋" is displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.900Z</t>
+    <t>2026-07-25T16:00:10.803Z</t>
   </si>
   <si>
     <t>DASH-APP-03</t>
@@ -818,7 +818,7 @@
     <t>Shimmer loading boxes appear while data is fetching</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.929Z</t>
+    <t>2026-07-25T16:00:10.833Z</t>
   </si>
   <si>
     <t>DASH-APP-04</t>
@@ -835,7 +835,7 @@
     <t>Total Volunteers card shows numeric count</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:01.958Z</t>
+    <t>2026-07-25T16:00:10.864Z</t>
   </si>
   <si>
     <t>DASH-APP-05</t>
@@ -851,7 +851,7 @@
     <t>Active Events card displays count</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:02.011Z</t>
+    <t>2026-07-25T16:00:10.895Z</t>
   </si>
   <si>
     <t>DASH-APP-06</t>
@@ -867,7 +867,7 @@
     <t>Hours This Month card renders with value</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:02.046Z</t>
+    <t>2026-07-25T16:00:10.926Z</t>
   </si>
   <si>
     <t>DASH-APP-07</t>
@@ -882,7 +882,7 @@
     <t>Attendance Rate card shows percentage value</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:02.080Z</t>
+    <t>2026-07-25T16:00:10.956Z</t>
   </si>
   <si>
     <t>DASH-APP-08</t>
@@ -897,7 +897,7 @@
     <t>All 4 stat cards have distinct gradient backgrounds</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:02.108Z</t>
+    <t>2026-07-25T16:00:10.988Z</t>
   </si>
   <si>
     <t>DASH-APP-09</t>
@@ -914,7 +914,7 @@
     <t>AI Insights banner shows volunteer recommendation text</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:02.143Z</t>
+    <t>2026-07-25T16:00:11.018Z</t>
   </si>
   <si>
     <t>DASH-APP-10</t>
@@ -930,7 +930,7 @@
     <t>AI Chat screen is displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:02.172Z</t>
+    <t>2026-07-25T16:00:11.049Z</t>
   </si>
   <si>
     <t>DASH-APP-11</t>
@@ -946,7 +946,7 @@
     <t>Volunteer Growth line chart renders with 9 months data</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:02.198Z</t>
+    <t>2026-07-25T16:00:11.080Z</t>
   </si>
   <si>
     <t>DASH-APP-12</t>
@@ -962,7 +962,7 @@
     <t>Category pie chart renders with slices</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:02.228Z</t>
+    <t>2026-07-25T16:00:11.110Z</t>
   </si>
   <si>
     <t>DASH-APP-13</t>
@@ -978,7 +978,7 @@
     <t>Weekly Attendance bar chart is displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:02.271Z</t>
+    <t>2026-07-25T16:00:11.140Z</t>
   </si>
   <si>
     <t>DASH-APP-14</t>
@@ -995,7 +995,7 @@
     <t>Recent Activity section shows at least 1 activity item</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:02.303Z</t>
+    <t>2026-07-25T16:00:11.171Z</t>
   </si>
   <si>
     <t>DASH-APP-15</t>
@@ -1010,7 +1010,7 @@
     <t>Activity items have all 3 content elements</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:02.336Z</t>
+    <t>2026-07-25T16:00:11.202Z</t>
   </si>
   <si>
     <t>DASH-APP-16</t>
@@ -1026,7 +1026,7 @@
     <t>Bottom nav bar shows all 6 navigation tabs</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:02.372Z</t>
+    <t>2026-07-25T16:00:11.233Z</t>
   </si>
   <si>
     <t>DASH-APP-17</t>
@@ -1042,7 +1042,7 @@
     <t>Volunteers screen is displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:02.400Z</t>
+    <t>2026-07-25T16:00:11.263Z</t>
   </si>
   <si>
     <t>DASH-APP-18</t>
@@ -1058,7 +1058,7 @@
     <t>Events screen is displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:02.435Z</t>
+    <t>2026-07-25T16:00:11.309Z</t>
   </si>
   <si>
     <t>DASH-APP-19</t>
@@ -1074,7 +1074,7 @@
     <t>Attendance screen is displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:02.469Z</t>
+    <t>2026-07-25T16:00:11.338Z</t>
   </si>
   <si>
     <t>DASH-APP-20</t>
@@ -1090,7 +1090,7 @@
     <t>Reports screen is displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:02.511Z</t>
+    <t>2026-07-25T16:00:11.369Z</t>
   </si>
   <si>
     <t>VOL-APP-01</t>
@@ -1107,7 +1107,7 @@
     <t>Volunteers screen renders with title and subtitle</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:02.553Z</t>
+    <t>2026-07-25T16:00:11.400Z</t>
   </si>
   <si>
     <t>VOL-APP-02</t>
@@ -1124,7 +1124,7 @@
     <t>Volunteer list renders with cards showing name and role</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:02.595Z</t>
+    <t>2026-07-25T16:00:11.431Z</t>
   </si>
   <si>
     <t>VOL-APP-03</t>
@@ -1141,7 +1141,7 @@
     <t>Shimmer placeholders appear during loading</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:02.629Z</t>
+    <t>2026-07-25T16:00:11.462Z</t>
   </si>
   <si>
     <t>VOL-APP-04</t>
@@ -1158,7 +1158,7 @@
     <t>Volunteer list filters by typed name</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:02.658Z</t>
+    <t>2026-07-25T16:00:11.493Z</t>
   </si>
   <si>
     <t>VOL-APP-05</t>
@@ -1174,7 +1174,7 @@
     <t>"No volunteers found" empty state is shown</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:02.694Z</t>
+    <t>2026-07-25T16:00:11.524Z</t>
   </si>
   <si>
     <t>VOL-APP-06</t>
@@ -1191,7 +1191,7 @@
     <t>Full volunteer list is restored after clearing search</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:02.733Z</t>
+    <t>2026-07-25T16:00:11.555Z</t>
   </si>
   <si>
     <t>VOL-APP-07</t>
@@ -1207,7 +1207,7 @@
     <t>Only active volunteers are displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:02.771Z</t>
+    <t>2026-07-25T16:00:11.586Z</t>
   </si>
   <si>
     <t>VOL-APP-08</t>
@@ -1223,7 +1223,7 @@
     <t>Only inactive volunteers are displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:02.805Z</t>
+    <t>2026-07-25T16:00:11.617Z</t>
   </si>
   <si>
     <t>VOL-APP-09</t>
@@ -1240,7 +1240,7 @@
     <t>All volunteers are shown when "All" filter is selected</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:02.844Z</t>
+    <t>2026-07-25T16:00:11.648Z</t>
   </si>
   <si>
     <t>VOL-APP-10</t>
@@ -1256,7 +1256,7 @@
     <t>Volunteer card contains avatar, name, role, and skills</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:02.886Z</t>
+    <t>2026-07-25T16:00:11.679Z</t>
   </si>
   <si>
     <t>VOL-APP-11</t>
@@ -1271,7 +1271,7 @@
     <t>Hours and events count are visible on each card</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:02.928Z</t>
+    <t>2026-07-25T16:00:11.710Z</t>
   </si>
   <si>
     <t>VOL-APP-12</t>
@@ -1287,7 +1287,7 @@
     <t>Status badges show correct colors per status</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:02.977Z</t>
+    <t>2026-07-25T16:00:11.741Z</t>
   </si>
   <si>
     <t>VOL-APP-13</t>
@@ -1303,7 +1303,7 @@
     <t>Add Volunteer dialog opens with all form fields</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:03.019Z</t>
+    <t>2026-07-25T16:00:11.773Z</t>
   </si>
   <si>
     <t>VOL-APP-14</t>
@@ -1320,7 +1320,7 @@
     <t>Required field validation errors are shown</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:03.066Z</t>
+    <t>2026-07-25T16:00:11.803Z</t>
   </si>
   <si>
     <t>VOL-APP-15</t>
@@ -1338,7 +1338,7 @@
     <t>New volunteer is added and "Volunteer added!" snackbar shown</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:03.096Z</t>
+    <t>2026-07-25T16:00:11.834Z</t>
   </si>
   <si>
     <t>VOL-APP-16</t>
@@ -1356,7 +1356,7 @@
     <t>Dialog closes without creating a new volunteer</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:03.137Z</t>
+    <t>2026-07-25T16:00:11.865Z</t>
   </si>
   <si>
     <t>VOL-APP-17</t>
@@ -1373,7 +1373,7 @@
     <t>Email validation error is displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:03.178Z</t>
+    <t>2026-07-25T16:00:11.895Z</t>
   </si>
   <si>
     <t>VOL-APP-18</t>
@@ -1390,7 +1390,7 @@
     <t>Volunteer detail sheet opens with full information</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:03.228Z</t>
+    <t>2026-07-25T16:00:11.926Z</t>
   </si>
   <si>
     <t>VOL-APP-19</t>
@@ -1407,7 +1407,7 @@
     <t>Skills list and events count are shown in detail view</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:03.275Z</t>
+    <t>2026-07-25T16:00:11.957Z</t>
   </si>
   <si>
     <t>VOL-APP-20</t>
@@ -1424,7 +1424,7 @@
     <t>Bottom sheet dismisses on downward swipe</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:03.323Z</t>
+    <t>2026-07-25T16:00:11.988Z</t>
   </si>
   <si>
     <t>VOL-APP-21</t>
@@ -1441,7 +1441,7 @@
     <t>Pull-to-refresh triggers data reload</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:03.379Z</t>
+    <t>2026-07-25T16:00:12.036Z</t>
   </si>
   <si>
     <t>VOL-APP-22</t>
@@ -1456,7 +1456,7 @@
     <t>Total volunteer count is visible on screen</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:03.435Z</t>
+    <t>2026-07-25T16:00:12.067Z</t>
   </si>
   <si>
     <t>EVT-APP-01</t>
@@ -1473,7 +1473,7 @@
     <t>Events screen renders correctly with title</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:03.497Z</t>
+    <t>2026-07-25T16:00:12.096Z</t>
   </si>
   <si>
     <t>EVT-APP-02</t>
@@ -1490,7 +1490,7 @@
     <t>Event cards render with title, location, and date</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:03.553Z</t>
+    <t>2026-07-25T16:00:12.127Z</t>
   </si>
   <si>
     <t>EVT-APP-03</t>
@@ -1506,7 +1506,7 @@
     <t>Shimmer boxes appear while events are loading</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:03.613Z</t>
+    <t>2026-07-25T16:00:12.157Z</t>
   </si>
   <si>
     <t>EVT-APP-04</t>
@@ -1523,7 +1523,7 @@
     <t>Events are filtered by search query</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:03.672Z</t>
+    <t>2026-07-25T16:00:12.188Z</t>
   </si>
   <si>
     <t>EVT-APP-05</t>
@@ -1539,7 +1539,7 @@
     <t>"No events found" empty state is displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:03.727Z</t>
+    <t>2026-07-25T16:00:12.219Z</t>
   </si>
   <si>
     <t>EVT-APP-06</t>
@@ -1555,7 +1555,7 @@
     <t>All events are listed when "All" filter is active</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:03.777Z</t>
+    <t>2026-07-25T16:00:12.250Z</t>
   </si>
   <si>
     <t>EVT-APP-07</t>
@@ -1572,7 +1572,7 @@
     <t>Only upcoming events are displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:03.816Z</t>
+    <t>2026-07-25T16:00:12.280Z</t>
   </si>
   <si>
     <t>EVT-APP-08</t>
@@ -1588,7 +1588,7 @@
     <t>Only completed events are displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:03.852Z</t>
+    <t>2026-07-25T16:00:12.312Z</t>
   </si>
   <si>
     <t>EVT-APP-09</t>
@@ -1604,7 +1604,7 @@
     <t>Only draft events are displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:03.894Z</t>
+    <t>2026-07-25T16:00:12.343Z</t>
   </si>
   <si>
     <t>EVT-APP-10</t>
@@ -1621,7 +1621,7 @@
     <t>Each event card shows title, category, and status badge</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:03.929Z</t>
+    <t>2026-07-25T16:00:12.373Z</t>
   </si>
   <si>
     <t>EVT-APP-11</t>
@@ -1637,7 +1637,7 @@
     <t>Location and date are shown on event cards</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:03.983Z</t>
+    <t>2026-07-25T16:00:12.404Z</t>
   </si>
   <si>
     <t>EVT-APP-12</t>
@@ -1653,7 +1653,7 @@
     <t>Fill rate progress bar and percentage are visible</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:04.032Z</t>
+    <t>2026-07-25T16:00:12.435Z</t>
   </si>
   <si>
     <t>EVT-APP-13</t>
@@ -1669,7 +1669,7 @@
     <t>Event list is scrollable without layout issues</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:04.068Z</t>
+    <t>2026-07-25T16:00:12.465Z</t>
   </si>
   <si>
     <t>EVT-APP-14</t>
@@ -1685,7 +1685,7 @@
     <t>New Event dialog opens with all form fields</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:04.115Z</t>
+    <t>2026-07-25T16:00:12.496Z</t>
   </si>
   <si>
     <t>EVT-APP-15</t>
@@ -1702,7 +1702,7 @@
     <t>"Required" validation error on empty required fields</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:04.151Z</t>
+    <t>2026-07-25T16:00:12.526Z</t>
   </si>
   <si>
     <t>EVT-APP-16</t>
@@ -1719,7 +1719,7 @@
     <t>Event is created and success snackbar appears</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:04.192Z</t>
+    <t>2026-07-25T16:00:12.557Z</t>
   </si>
   <si>
     <t>EVT-APP-17</t>
@@ -1736,7 +1736,7 @@
     <t>All 6 categories (Education, Food Security, Environment, Health, Housing, Digital) visible</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:04.248Z</t>
+    <t>2026-07-25T16:00:12.588Z</t>
   </si>
   <si>
     <t>EVT-APP-18</t>
@@ -1754,7 +1754,7 @@
     <t>Dialog closes without creating an event</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:04.297Z</t>
+    <t>2026-07-25T16:00:12.619Z</t>
   </si>
   <si>
     <t>EVT-APP-19</t>
@@ -1771,7 +1771,7 @@
     <t>Event detail bottom sheet opens with full details</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:04.375Z</t>
+    <t>2026-07-25T16:00:12.666Z</t>
   </si>
   <si>
     <t>EVT-APP-20</t>
@@ -1787,7 +1787,7 @@
     <t>All event metadata is shown in detail sheet</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:04.422Z</t>
+    <t>2026-07-25T16:00:12.697Z</t>
   </si>
   <si>
     <t>EVT-APP-21</t>
@@ -1803,7 +1803,7 @@
     <t>KPI cards for volunteers registered and attended are visible</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:04.458Z</t>
+    <t>2026-07-25T16:00:12.728Z</t>
   </si>
   <si>
     <t>EVT-APP-22</t>
@@ -1819,7 +1819,7 @@
     <t>Tag chips are displayed in event detail</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:04.491Z</t>
+    <t>2026-07-25T16:00:12.759Z</t>
   </si>
   <si>
     <t>EVT-APP-23</t>
@@ -1836,7 +1836,7 @@
     <t>Manage Volunteers button is functional and closes the sheet</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:04.541Z</t>
+    <t>2026-07-25T16:00:12.791Z</t>
   </si>
   <si>
     <t>EVT-APP-24</t>
@@ -1853,7 +1853,7 @@
     <t>Bottom sheet expands and collapses on drag</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:04.589Z</t>
+    <t>2026-07-25T16:00:12.821Z</t>
   </si>
   <si>
     <t>ATT-APP-01</t>
@@ -1870,7 +1870,7 @@
     <t>Attendance screen renders with correct title and subtitle</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:04.638Z</t>
+    <t>2026-07-25T16:00:12.868Z</t>
   </si>
   <si>
     <t>ATT-APP-02</t>
@@ -1886,7 +1886,7 @@
     <t>Shimmer loading boxes appear during data fetch</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:04.670Z</t>
+    <t>2026-07-25T16:00:12.899Z</t>
   </si>
   <si>
     <t>ATT-APP-03</t>
@@ -1902,7 +1902,7 @@
     <t>All 4 summary chips render with numeric/percentage values</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:04.719Z</t>
+    <t>2026-07-25T16:00:12.929Z</t>
   </si>
   <si>
     <t>ATT-APP-04</t>
@@ -1920,7 +1920,7 @@
     <t>Each summary chip has the correct color coding</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:04.768Z</t>
+    <t>2026-07-25T16:00:12.960Z</t>
   </si>
   <si>
     <t>ATT-APP-05</t>
@@ -1936,7 +1936,7 @@
     <t>Tab bar renders with both tabs, Recent Records active by default</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:04.823Z</t>
+    <t>2026-07-25T16:00:12.990Z</t>
   </si>
   <si>
     <t>ATT-APP-06</t>
@@ -1953,7 +1953,7 @@
     <t>"By Event" tab shows attendance grouped by events</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:04.870Z</t>
+    <t>2026-07-25T16:00:13.021Z</t>
   </si>
   <si>
     <t>ATT-APP-07</t>
@@ -1969,7 +1969,7 @@
     <t>Recent Records tab shows individual check-in entries</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:04.914Z</t>
+    <t>2026-07-25T16:00:13.066Z</t>
   </si>
   <si>
     <t>ATT-APP-08</t>
@@ -1985,7 +1985,7 @@
     <t>Records list shows volunteer name, event, status icon</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:04.950Z</t>
+    <t>2026-07-25T16:00:13.097Z</t>
   </si>
   <si>
     <t>ATT-APP-09</t>
@@ -2002,7 +2002,7 @@
     <t>Status icons match the attendance status correctly</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:04.990Z</t>
+    <t>2026-07-25T16:00:13.128Z</t>
   </si>
   <si>
     <t>ATT-APP-10</t>
@@ -2018,7 +2018,7 @@
     <t>Check-in time and hours logged are shown on records</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:05.039Z</t>
+    <t>2026-07-25T16:00:13.159Z</t>
   </si>
   <si>
     <t>ATT-APP-11</t>
@@ -2034,7 +2034,7 @@
     <t>Records filter by volunteer name search query</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:05.101Z</t>
+    <t>2026-07-25T16:00:13.206Z</t>
   </si>
   <si>
     <t>ATT-APP-12</t>
@@ -2050,7 +2050,7 @@
     <t>Records filter by event name search query</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:05.150Z</t>
+    <t>2026-07-25T16:00:13.238Z</t>
   </si>
   <si>
     <t>ATT-APP-13</t>
@@ -2066,7 +2066,7 @@
     <t>"No records yet" empty state is shown for no results</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:05.191Z</t>
+    <t>2026-07-25T16:00:13.268Z</t>
   </si>
   <si>
     <t>ATT-APP-14</t>
@@ -2082,7 +2082,7 @@
     <t>Only present attendance records are displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:05.240Z</t>
+    <t>2026-07-25T16:00:13.298Z</t>
   </si>
   <si>
     <t>ATT-APP-15</t>
@@ -2098,7 +2098,7 @@
     <t>Only late attendance records are displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:05.282Z</t>
+    <t>2026-07-25T16:00:13.330Z</t>
   </si>
   <si>
     <t>ATT-APP-16</t>
@@ -2114,7 +2114,7 @@
     <t>Only absent records are displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:05.325Z</t>
+    <t>2026-07-25T16:00:13.376Z</t>
   </si>
   <si>
     <t>ATT-APP-17</t>
@@ -2131,7 +2131,7 @@
     <t>All attendance records are shown on "All" filter</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:05.372Z</t>
+    <t>2026-07-25T16:00:13.406Z</t>
   </si>
   <si>
     <t>ATT-APP-18</t>
@@ -2147,7 +2147,7 @@
     <t>Check-In dialog opens with form fields</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:05.412Z</t>
+    <t>2026-07-25T16:00:13.437Z</t>
   </si>
   <si>
     <t>ATT-APP-19</t>
@@ -2165,7 +2165,7 @@
     <t>"[Name] checked in successfully!" snackbar is shown</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:05.469Z</t>
+    <t>2026-07-25T16:00:13.468Z</t>
   </si>
   <si>
     <t>ATT-APP-20</t>
@@ -2182,7 +2182,7 @@
     <t>Check-in is blocked when name field is empty</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:05.525Z</t>
+    <t>2026-07-25T16:00:13.499Z</t>
   </si>
   <si>
     <t>ATT-APP-21</t>
@@ -2199,7 +2199,7 @@
     <t>Event dropdown shows all available events</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:05.574Z</t>
+    <t>2026-07-25T16:00:13.544Z</t>
   </si>
   <si>
     <t>ATT-APP-22</t>
@@ -2216,7 +2216,7 @@
     <t>Dialog closes on Cancel without performing check-in</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:05.629Z</t>
+    <t>2026-07-25T16:00:13.575Z</t>
   </si>
   <si>
     <t>ATT-APP-23</t>
@@ -2232,7 +2232,7 @@
     <t>Each past event shows title, date, attendance rate, and progress bar</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:05.671Z</t>
+    <t>2026-07-25T16:00:13.608Z</t>
   </si>
   <si>
     <t>ATT-APP-24</t>
@@ -2249,7 +2249,7 @@
     <t>Progress bar colors reflect attendance rate correctly</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:05.733Z</t>
+    <t>2026-07-25T16:00:13.639Z</t>
   </si>
   <si>
     <t>ATT-APP-25</t>
@@ -2265,7 +2265,7 @@
     <t>"No past events" empty state is shown</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:05.782Z</t>
+    <t>2026-07-25T16:00:13.685Z</t>
   </si>
   <si>
     <t>REP-APP-01</t>
@@ -2281,7 +2281,7 @@
     <t>Reports screen loads and title is displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:05.836Z</t>
+    <t>2026-07-25T16:00:13.734Z</t>
   </si>
   <si>
     <t>REP-APP-02</t>
@@ -2296,7 +2296,7 @@
     <t>All 4 KPI cards render with values</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:05.886Z</t>
+    <t>2026-07-25T16:00:13.824Z</t>
   </si>
   <si>
     <t>REP-APP-03</t>
@@ -2312,7 +2312,7 @@
     <t>Volunteer hours chart is displayed with data</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:05.929Z</t>
+    <t>2026-07-25T16:00:13.901Z</t>
   </si>
   <si>
     <t>REP-APP-04</t>
@@ -2327,7 +2327,7 @@
     <t>Attendance trend chart is visible</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:05.976Z</t>
+    <t>2026-07-25T16:00:13.946Z</t>
   </si>
   <si>
     <t>REP-APP-05</t>
@@ -2342,7 +2342,7 @@
     <t>Category chart is visible</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:06.019Z</t>
+    <t>2026-07-25T16:00:13.994Z</t>
   </si>
   <si>
     <t>REP-APP-06</t>
@@ -2359,7 +2359,7 @@
     <t>Report data reflects This Week range</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:06.066Z</t>
+    <t>2026-07-25T16:00:14.039Z</t>
   </si>
   <si>
     <t>REP-APP-07</t>
@@ -2375,7 +2375,7 @@
     <t>Report reflects This Month data</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:06.116Z</t>
+    <t>2026-07-25T16:00:14.085Z</t>
   </si>
   <si>
     <t>REP-APP-08</t>
@@ -2391,7 +2391,7 @@
     <t>Report reflects Last 3 Months data</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:06.157Z</t>
+    <t>2026-07-25T16:00:14.131Z</t>
   </si>
   <si>
     <t>REP-APP-09</t>
@@ -2407,7 +2407,7 @@
     <t>Report reflects This Year data</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:06.226Z</t>
+    <t>2026-07-25T16:00:14.177Z</t>
   </si>
   <si>
     <t>REP-APP-10</t>
@@ -2423,7 +2423,7 @@
     <t>Export dialog or share sheet is displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:06.275Z</t>
+    <t>2026-07-25T16:00:14.223Z</t>
   </si>
   <si>
     <t>REP-APP-11</t>
@@ -2439,7 +2439,7 @@
     <t>Top volunteers list renders with names and hours</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:06.323Z</t>
+    <t>2026-07-25T16:00:14.268Z</t>
   </si>
   <si>
     <t>REP-APP-12</t>
@@ -2454,7 +2454,7 @@
     <t>Skills distribution chart renders correctly</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:06.366Z</t>
+    <t>2026-07-25T16:00:14.298Z</t>
   </si>
   <si>
     <t>REP-APP-13</t>
@@ -2470,7 +2470,7 @@
     <t>Shimmer placeholders appear during data fetch</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:06.414Z</t>
+    <t>2026-07-25T16:00:14.344Z</t>
   </si>
   <si>
     <t>REP-APP-14</t>
@@ -2487,7 +2487,7 @@
     <t>Reports data refreshes successfully</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:06.469Z</t>
+    <t>2026-07-25T16:00:14.390Z</t>
   </si>
   <si>
     <t>REP-APP-15</t>
@@ -2502,7 +2502,7 @@
     <t>All KPI values are numeric and greater than zero</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:06.518Z</t>
+    <t>2026-07-25T16:00:14.436Z</t>
   </si>
   <si>
     <t>SET-APP-01</t>
@@ -2519,7 +2519,7 @@
     <t>Settings screen renders with title and subtitle</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:06.560Z</t>
+    <t>2026-07-25T16:00:14.481Z</t>
   </si>
   <si>
     <t>SET-APP-02</t>
@@ -2535,7 +2535,7 @@
     <t>Profile card shows all user information</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:06.615Z</t>
+    <t>2026-07-25T16:00:14.527Z</t>
   </si>
   <si>
     <t>SET-APP-03</t>
@@ -2552,7 +2552,7 @@
     <t>All 3 profile info rows are displayed with values</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:06.664Z</t>
+    <t>2026-07-25T16:00:14.572Z</t>
   </si>
   <si>
     <t>SET-APP-04</t>
@@ -2568,7 +2568,7 @@
     <t>Notifications section has all 4 toggle switches</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:06.707Z</t>
+    <t>2026-07-25T16:00:14.617Z</t>
   </si>
   <si>
     <t>SET-APP-05</t>
@@ -2586,7 +2586,7 @@
     <t>Email notifications toggle changes state on tap</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:06.754Z</t>
+    <t>2026-07-25T16:00:14.665Z</t>
   </si>
   <si>
     <t>SET-APP-06</t>
@@ -2602,7 +2602,7 @@
     <t>Push notifications toggle is functional</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:06.803Z</t>
+    <t>2026-07-25T16:00:14.710Z</t>
   </si>
   <si>
     <t>SET-APP-07</t>
@@ -2618,7 +2618,7 @@
     <t>AI insights toggle is functional</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:06.851Z</t>
+    <t>2026-07-25T16:00:14.741Z</t>
   </si>
   <si>
     <t>SET-APP-08</t>
@@ -2634,7 +2634,7 @@
     <t>Weekly digest toggle is functional</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:06.907Z</t>
+    <t>2026-07-25T16:00:14.788Z</t>
   </si>
   <si>
     <t>SET-APP-09</t>
@@ -2651,7 +2651,7 @@
     <t>Security section shows 2FA toggle and Change Password option</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:06.947Z</t>
+    <t>2026-07-25T16:00:14.834Z</t>
   </si>
   <si>
     <t>SET-APP-10</t>
@@ -2667,7 +2667,7 @@
     <t>2FA toggle is functional</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:06.997Z</t>
+    <t>2026-07-25T16:00:14.881Z</t>
   </si>
   <si>
     <t>SET-APP-11</t>
@@ -2683,7 +2683,7 @@
     <t>Password reset email is triggered and snackbar shown</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:07.045Z</t>
+    <t>2026-07-25T16:00:14.929Z</t>
   </si>
   <si>
     <t>SET-APP-12</t>
@@ -2700,7 +2700,7 @@
     <t>Language and Timezone dropdowns are visible</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:07.102Z</t>
+    <t>2026-07-25T16:00:14.975Z</t>
   </si>
   <si>
     <t>SET-APP-13</t>
@@ -2716,7 +2716,7 @@
     <t>Language dropdown shows all 4 supported languages</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:07.159Z</t>
+    <t>2026-07-25T16:00:15.021Z</t>
   </si>
   <si>
     <t>SET-APP-14</t>
@@ -2732,7 +2732,7 @@
     <t>Timezone dropdown shows all 4 US timezone options</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:07.206Z</t>
+    <t>2026-07-25T16:00:15.068Z</t>
   </si>
   <si>
     <t>SET-APP-15</t>
@@ -2749,7 +2749,7 @@
     <t>Language selection is reflected in the dropdown</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:07.254Z</t>
+    <t>2026-07-25T16:00:15.114Z</t>
   </si>
   <si>
     <t>SET-APP-16</t>
@@ -2765,7 +2765,7 @@
     <t>About section shows all 4 info tiles</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:07.298Z</t>
+    <t>2026-07-25T16:00:15.160Z</t>
   </si>
   <si>
     <t>SET-APP-17</t>
@@ -2780,7 +2780,7 @@
     <t>App version is displayed as "1.0.0"</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:07.345Z</t>
+    <t>2026-07-25T16:00:15.223Z</t>
   </si>
   <si>
     <t>SET-APP-18</t>
@@ -2796,7 +2796,7 @@
     <t>"Coming soon!" snackbar is shown</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:07.400Z</t>
+    <t>2026-07-25T16:00:15.270Z</t>
   </si>
   <si>
     <t>SET-APP-19</t>
@@ -2809,7 +2809,7 @@
 2. Assert snackbar appears</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:07.457Z</t>
+    <t>2026-07-25T16:00:15.315Z</t>
   </si>
   <si>
     <t>SET-APP-20</t>
@@ -2825,7 +2825,7 @@
     <t>Snackbar shows "Contact: support@volunteersync.io"</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:07.511Z</t>
+    <t>2026-07-25T16:00:15.361Z</t>
   </si>
   <si>
     <t>SET-APP-21</t>
@@ -2838,7 +2838,7 @@
 2. Assert "Sign Out" outlined button visible</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:07.585Z</t>
+    <t>2026-07-25T16:00:15.407Z</t>
   </si>
   <si>
     <t>SET-APP-22</t>
@@ -2855,7 +2855,7 @@
     <t>User is signed out and Login screen is displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:07.633Z</t>
+    <t>2026-07-25T16:00:15.454Z</t>
   </si>
   <si>
     <t>SET-APP-23</t>
@@ -2871,7 +2871,7 @@
     <t>Footer attribution text is displayed at bottom of Settings</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:07.679Z</t>
+    <t>2026-07-25T16:00:15.500Z</t>
   </si>
   <si>
     <t>AI-APP-01</t>
@@ -2887,7 +2887,7 @@
     <t>AI Chat screen loads with correct header</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:07.728Z</t>
+    <t>2026-07-25T16:00:15.546Z</t>
   </si>
   <si>
     <t>AI-APP-02</t>
@@ -2903,7 +2903,7 @@
     <t>Volt AI welcome message is displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:07.782Z</t>
+    <t>2026-07-25T16:00:15.592Z</t>
   </si>
   <si>
     <t>AI-APP-03</t>
@@ -2919,7 +2919,7 @@
     <t>Message input field is visible with placeholder text</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:07.837Z</t>
+    <t>2026-07-25T16:00:15.638Z</t>
   </si>
   <si>
     <t>AI-APP-04</t>
@@ -2936,7 +2936,7 @@
     <t>Typed text appears in the input field</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:07.900Z</t>
+    <t>2026-07-25T16:00:15.685Z</t>
   </si>
   <si>
     <t>AI-APP-05</t>
@@ -2953,7 +2953,7 @@
     <t>User message is sent and appears in chat as user bubble</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:07.955Z</t>
+    <t>2026-07-25T16:00:15.731Z</t>
   </si>
   <si>
     <t>AI-APP-06</t>
@@ -2970,7 +2970,7 @@
     <t>AI response is received and displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:08.011Z</t>
+    <t>2026-07-25T16:00:15.777Z</t>
   </si>
   <si>
     <t>AI-APP-07</t>
@@ -2987,7 +2987,7 @@
     <t>User and AI messages have visually distinct bubble styles</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:08.068Z</t>
+    <t>2026-07-25T16:00:15.823Z</t>
   </si>
   <si>
     <t>AI-APP-08</t>
@@ -3003,7 +3003,7 @@
     <t>Loading indicator appears while AI generates response</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:08.129Z</t>
+    <t>2026-07-25T16:00:15.868Z</t>
   </si>
   <si>
     <t>AI-APP-09</t>
@@ -3020,7 +3020,7 @@
     <t>Input field is cleared after sending</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:08.170Z</t>
+    <t>2026-07-25T16:00:15.915Z</t>
   </si>
   <si>
     <t>AI-APP-10</t>
@@ -3036,7 +3036,7 @@
     <t>Chat auto-scrolls to the latest message</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:08.240Z</t>
+    <t>2026-07-25T16:00:15.961Z</t>
   </si>
   <si>
     <t>AI-APP-11</t>
@@ -3053,7 +3053,7 @@
     <t>Quick prompt chips are functional</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:08.302Z</t>
+    <t>2026-07-25T16:00:16.006Z</t>
   </si>
   <si>
     <t>AI-APP-12</t>
@@ -3071,7 +3071,7 @@
     <t>Chat messages are preserved when revisiting the screen</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:08.365Z</t>
+    <t>2026-07-25T16:00:16.053Z</t>
   </si>
   <si>
     <t>AI-APP-13</t>
@@ -3088,7 +3088,7 @@
     <t>Chat history is cleared after reset</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:08.434Z</t>
+    <t>2026-07-25T16:00:16.099Z</t>
   </si>
   <si>
     <t>AI-APP-14</t>
@@ -3105,7 +3105,7 @@
     <t>Empty message is not sent</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:08.484Z</t>
+    <t>2026-07-25T16:00:16.145Z</t>
   </si>
   <si>
     <t>AI-APP-15</t>
@@ -3122,7 +3122,7 @@
     <t>Back navigation returns to previous screen</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:08.560Z</t>
+    <t>2026-07-25T16:00:16.191Z</t>
   </si>
   <si>
     <t>LND-APP-11</t>
@@ -3142,7 +3142,7 @@
     <t>Mobile app behaves correctly for Performance capability #11</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:08.600Z</t>
+    <t>2026-07-25T16:00:16.223Z</t>
   </si>
   <si>
     <t>LND-APP-12</t>
@@ -3162,7 +3162,7 @@
     <t>Mobile app behaves correctly for Security capability #12</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:08.653Z</t>
+    <t>2026-07-25T16:00:16.256Z</t>
   </si>
   <si>
     <t>LND-APP-13</t>
@@ -3179,7 +3179,7 @@
     <t>Mobile app behaves correctly for Accessibility capability #13</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:08.685Z</t>
+    <t>2026-07-25T16:00:16.281Z</t>
   </si>
   <si>
     <t>LND-APP-14</t>
@@ -3196,7 +3196,7 @@
     <t>Mobile app behaves correctly for UI Visibility capability #14</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:08.718Z</t>
+    <t>2026-07-25T16:00:16.312Z</t>
   </si>
   <si>
     <t>LND-APP-15</t>
@@ -3213,7 +3213,7 @@
     <t>Mobile app behaves correctly for Functional capability #15</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:08.759Z</t>
+    <t>2026-07-25T16:00:16.336Z</t>
   </si>
   <si>
     <t>LND-APP-16</t>
@@ -3230,7 +3230,7 @@
     <t>Mobile app behaves correctly for Validation capability #16</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:08.796Z</t>
+    <t>2026-07-25T16:00:16.362Z</t>
   </si>
   <si>
     <t>LND-APP-17</t>
@@ -3250,7 +3250,7 @@
     <t>Mobile app behaves correctly for Responsive capability #17</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:08.831Z</t>
+    <t>2026-07-25T16:00:16.388Z</t>
   </si>
   <si>
     <t>LND-APP-18</t>
@@ -3267,7 +3267,7 @@
     <t>Mobile app behaves correctly for Performance capability #18</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:08.875Z</t>
+    <t>2026-07-25T16:00:16.415Z</t>
   </si>
   <si>
     <t>LND-APP-19</t>
@@ -3284,7 +3284,7 @@
     <t>Mobile app behaves correctly for Security capability #19</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:08.922Z</t>
+    <t>2026-07-25T16:00:16.445Z</t>
   </si>
   <si>
     <t>LND-APP-20</t>
@@ -3301,7 +3301,7 @@
     <t>Mobile app behaves correctly for Accessibility capability #20</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:08.966Z</t>
+    <t>2026-07-25T16:00:16.472Z</t>
   </si>
   <si>
     <t>LND-APP-21</t>
@@ -3318,7 +3318,7 @@
     <t>Mobile app behaves correctly for UI Visibility capability #21</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:09.001Z</t>
+    <t>2026-07-25T16:00:16.499Z</t>
   </si>
   <si>
     <t>LND-APP-22</t>
@@ -3335,7 +3335,7 @@
     <t>Mobile app behaves correctly for Functional capability #22</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:09.033Z</t>
+    <t>2026-07-25T16:00:16.524Z</t>
   </si>
   <si>
     <t>LND-APP-23</t>
@@ -3352,7 +3352,7 @@
     <t>Mobile app behaves correctly for Validation capability #23</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:09.068Z</t>
+    <t>2026-07-25T16:00:16.552Z</t>
   </si>
   <si>
     <t>LND-APP-24</t>
@@ -3369,7 +3369,7 @@
     <t>Mobile app behaves correctly for Responsive capability #24</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:09.104Z</t>
+    <t>2026-07-25T16:00:16.579Z</t>
   </si>
   <si>
     <t>LND-APP-25</t>
@@ -3386,7 +3386,7 @@
     <t>Mobile app behaves correctly for Performance capability #25</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:09.153Z</t>
+    <t>2026-07-25T16:00:16.609Z</t>
   </si>
   <si>
     <t>LND-APP-26</t>
@@ -3403,7 +3403,7 @@
     <t>Mobile app behaves correctly for Security capability #26</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:09.195Z</t>
+    <t>2026-07-25T16:00:16.638Z</t>
   </si>
   <si>
     <t>LND-APP-27</t>
@@ -3420,7 +3420,7 @@
     <t>Mobile app behaves correctly for Accessibility capability #27</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:09.229Z</t>
+    <t>2026-07-25T16:00:16.665Z</t>
   </si>
   <si>
     <t>LND-APP-28</t>
@@ -3437,7 +3437,7 @@
     <t>Mobile app behaves correctly for UI Visibility capability #28</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:09.273Z</t>
+    <t>2026-07-25T16:00:16.692Z</t>
   </si>
   <si>
     <t>LND-APP-29</t>
@@ -3454,7 +3454,7 @@
     <t>Mobile app behaves correctly for Functional capability #29</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:09.317Z</t>
+    <t>2026-07-25T16:00:16.745Z</t>
   </si>
   <si>
     <t>LND-APP-30</t>
@@ -3471,7 +3471,7 @@
     <t>Mobile app behaves correctly for Validation capability #30</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:09.359Z</t>
+    <t>2026-07-25T16:00:16.783Z</t>
   </si>
   <si>
     <t>LND-APP-31</t>
@@ -3488,7 +3488,7 @@
     <t>Mobile app behaves correctly for Responsive capability #31</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:09.394Z</t>
+    <t>2026-07-25T16:00:16.814Z</t>
   </si>
   <si>
     <t>LND-APP-32</t>
@@ -3505,7 +3505,7 @@
     <t>Mobile app behaves correctly for Performance capability #32</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:09.428Z</t>
+    <t>2026-07-25T16:00:16.842Z</t>
   </si>
   <si>
     <t>LND-APP-33</t>
@@ -3522,7 +3522,7 @@
     <t>Mobile app behaves correctly for Security capability #33</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:09.473Z</t>
+    <t>2026-07-25T16:00:16.874Z</t>
   </si>
   <si>
     <t>LND-APP-34</t>
@@ -3539,7 +3539,7 @@
     <t>Mobile app behaves correctly for Accessibility capability #34</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:09.526Z</t>
+    <t>2026-07-25T16:00:16.905Z</t>
   </si>
   <si>
     <t>LND-APP-35</t>
@@ -3556,7 +3556,7 @@
     <t>Mobile app behaves correctly for UI Visibility capability #35</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:09.568Z</t>
+    <t>2026-07-25T16:00:16.940Z</t>
   </si>
   <si>
     <t>LND-APP-36</t>
@@ -3573,7 +3573,7 @@
     <t>Mobile app behaves correctly for Functional capability #36</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:09.615Z</t>
+    <t>2026-07-25T16:00:16.973Z</t>
   </si>
   <si>
     <t>LOG-APP-13</t>
@@ -3587,7 +3587,7 @@
 3. Verify Accessibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:09.653Z</t>
+    <t>2026-07-25T16:00:17.004Z</t>
   </si>
   <si>
     <t>LOG-APP-14</t>
@@ -3601,7 +3601,7 @@
 3. Verify UI Visibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:09.696Z</t>
+    <t>2026-07-25T16:00:17.030Z</t>
   </si>
   <si>
     <t>LOG-APP-15</t>
@@ -3615,7 +3615,7 @@
 3. Verify Functional response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:09.740Z</t>
+    <t>2026-07-25T16:00:17.062Z</t>
   </si>
   <si>
     <t>LOG-APP-16</t>
@@ -3629,7 +3629,7 @@
 3. Verify Validation response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:09.780Z</t>
+    <t>2026-07-25T16:00:17.094Z</t>
   </si>
   <si>
     <t>LOG-APP-17</t>
@@ -3643,7 +3643,7 @@
 3. Verify Responsive response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:09.819Z</t>
+    <t>2026-07-25T16:00:17.126Z</t>
   </si>
   <si>
     <t>LOG-APP-18</t>
@@ -3657,7 +3657,7 @@
 3. Verify Performance response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:09.865Z</t>
+    <t>2026-07-25T16:00:17.155Z</t>
   </si>
   <si>
     <t>LOG-APP-19</t>
@@ -3671,7 +3671,7 @@
 3. Verify Security response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:09.913Z</t>
+    <t>2026-07-25T16:00:17.184Z</t>
   </si>
   <si>
     <t>LOG-APP-20</t>
@@ -3685,7 +3685,7 @@
 3. Verify Accessibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:09.954Z</t>
+    <t>2026-07-25T16:00:17.216Z</t>
   </si>
   <si>
     <t>LOG-APP-21</t>
@@ -3699,7 +3699,7 @@
 3. Verify UI Visibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:09.999Z</t>
+    <t>2026-07-25T16:00:17.255Z</t>
   </si>
   <si>
     <t>LOG-APP-22</t>
@@ -3713,7 +3713,7 @@
 3. Verify Functional response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:10.043Z</t>
+    <t>2026-07-25T16:00:17.284Z</t>
   </si>
   <si>
     <t>LOG-APP-23</t>
@@ -3727,7 +3727,7 @@
 3. Verify Validation response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:10.081Z</t>
+    <t>2026-07-25T16:00:17.315Z</t>
   </si>
   <si>
     <t>LOG-APP-24</t>
@@ -3741,7 +3741,7 @@
 3. Verify Responsive response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:10.119Z</t>
+    <t>2026-07-25T16:00:17.347Z</t>
   </si>
   <si>
     <t>LOG-APP-25</t>
@@ -3755,7 +3755,7 @@
 3. Verify Performance response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:10.162Z</t>
+    <t>2026-07-25T16:00:17.376Z</t>
   </si>
   <si>
     <t>LOG-APP-26</t>
@@ -3769,7 +3769,7 @@
 3. Verify Security response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:10.217Z</t>
+    <t>2026-07-25T16:00:17.411Z</t>
   </si>
   <si>
     <t>LOG-APP-27</t>
@@ -3783,7 +3783,7 @@
 3. Verify Accessibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:10.277Z</t>
+    <t>2026-07-25T16:00:17.445Z</t>
   </si>
   <si>
     <t>LOG-APP-28</t>
@@ -3797,7 +3797,7 @@
 3. Verify UI Visibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:10.335Z</t>
+    <t>2026-07-25T16:00:17.482Z</t>
   </si>
   <si>
     <t>LOG-APP-29</t>
@@ -3811,7 +3811,7 @@
 3. Verify Functional response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:10.398Z</t>
+    <t>2026-07-25T16:00:17.512Z</t>
   </si>
   <si>
     <t>LOG-APP-30</t>
@@ -3825,7 +3825,7 @@
 3. Verify Validation response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:10.437Z</t>
+    <t>2026-07-25T16:00:17.543Z</t>
   </si>
   <si>
     <t>LOG-APP-31</t>
@@ -3839,7 +3839,7 @@
 3. Verify Responsive response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:10.477Z</t>
+    <t>2026-07-25T16:00:17.576Z</t>
   </si>
   <si>
     <t>LOG-APP-32</t>
@@ -3853,7 +3853,7 @@
 3. Verify Performance response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:10.515Z</t>
+    <t>2026-07-25T16:00:17.610Z</t>
   </si>
   <si>
     <t>LOG-APP-33</t>
@@ -3867,7 +3867,7 @@
 3. Verify Security response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:10.555Z</t>
+    <t>2026-07-25T16:00:17.644Z</t>
   </si>
   <si>
     <t>LOG-APP-34</t>
@@ -3881,7 +3881,7 @@
 3. Verify Accessibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:10.600Z</t>
+    <t>2026-07-25T16:00:17.676Z</t>
   </si>
   <si>
     <t>LOG-APP-35</t>
@@ -3895,7 +3895,7 @@
 3. Verify UI Visibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:10.648Z</t>
+    <t>2026-07-25T16:00:17.707Z</t>
   </si>
   <si>
     <t>LOG-APP-36</t>
@@ -3909,7 +3909,7 @@
 3. Verify Functional response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:10.690Z</t>
+    <t>2026-07-25T16:00:17.742Z</t>
   </si>
   <si>
     <t>REG-APP-11</t>
@@ -3923,7 +3923,7 @@
 3. Verify Performance response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:10.743Z</t>
+    <t>2026-07-25T16:00:17.777Z</t>
   </si>
   <si>
     <t>REG-APP-12</t>
@@ -3937,7 +3937,7 @@
 3. Verify Security response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:10.806Z</t>
+    <t>2026-07-25T16:00:17.820Z</t>
   </si>
   <si>
     <t>REG-APP-13</t>
@@ -3951,7 +3951,7 @@
 3. Verify Accessibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:10.847Z</t>
+    <t>2026-07-25T16:00:17.852Z</t>
   </si>
   <si>
     <t>REG-APP-14</t>
@@ -3965,7 +3965,7 @@
 3. Verify UI Visibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:10.888Z</t>
+    <t>2026-07-25T16:00:17.888Z</t>
   </si>
   <si>
     <t>REG-APP-15</t>
@@ -3979,7 +3979,7 @@
 3. Verify Functional response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:10.937Z</t>
+    <t>2026-07-25T16:00:17.921Z</t>
   </si>
   <si>
     <t>REG-APP-16</t>
@@ -3993,7 +3993,7 @@
 3. Verify Validation response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:10.998Z</t>
+    <t>2026-07-25T16:00:17.956Z</t>
   </si>
   <si>
     <t>REG-APP-17</t>
@@ -4007,7 +4007,7 @@
 3. Verify Responsive response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:11.052Z</t>
+    <t>2026-07-25T16:00:17.992Z</t>
   </si>
   <si>
     <t>REG-APP-18</t>
@@ -4021,7 +4021,7 @@
 3. Verify Performance response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:11.108Z</t>
+    <t>2026-07-25T16:00:18.025Z</t>
   </si>
   <si>
     <t>REG-APP-19</t>
@@ -4035,7 +4035,7 @@
 3. Verify Security response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:11.157Z</t>
+    <t>2026-07-25T16:00:18.056Z</t>
   </si>
   <si>
     <t>REG-APP-20</t>
@@ -4049,7 +4049,7 @@
 3. Verify Accessibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:11.207Z</t>
+    <t>2026-07-25T16:00:18.091Z</t>
   </si>
   <si>
     <t>REG-APP-21</t>
@@ -4063,7 +4063,7 @@
 3. Verify UI Visibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:11.274Z</t>
+    <t>2026-07-25T16:00:18.133Z</t>
   </si>
   <si>
     <t>REG-APP-22</t>
@@ -4077,7 +4077,7 @@
 3. Verify Functional response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:11.331Z</t>
+    <t>2026-07-25T16:00:18.169Z</t>
   </si>
   <si>
     <t>REG-APP-23</t>
@@ -4091,7 +4091,7 @@
 3. Verify Validation response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:11.388Z</t>
+    <t>2026-07-25T16:00:18.204Z</t>
   </si>
   <si>
     <t>REG-APP-24</t>
@@ -4105,7 +4105,7 @@
 3. Verify Responsive response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:11.453Z</t>
+    <t>2026-07-25T16:00:18.239Z</t>
   </si>
   <si>
     <t>REG-APP-25</t>
@@ -4119,7 +4119,7 @@
 3. Verify Performance response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:11.518Z</t>
+    <t>2026-07-25T16:00:18.270Z</t>
   </si>
   <si>
     <t>REG-APP-26</t>
@@ -4133,7 +4133,7 @@
 3. Verify Security response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:11.584Z</t>
+    <t>2026-07-25T16:00:18.302Z</t>
   </si>
   <si>
     <t>REG-APP-27</t>
@@ -4147,7 +4147,7 @@
 3. Verify Accessibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:11.642Z</t>
+    <t>2026-07-25T16:00:18.335Z</t>
   </si>
   <si>
     <t>REG-APP-28</t>
@@ -4161,7 +4161,7 @@
 3. Verify UI Visibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:11.699Z</t>
+    <t>2026-07-25T16:00:18.366Z</t>
   </si>
   <si>
     <t>REG-APP-29</t>
@@ -4175,7 +4175,7 @@
 3. Verify Functional response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:11.762Z</t>
+    <t>2026-07-25T16:00:18.403Z</t>
   </si>
   <si>
     <t>REG-APP-30</t>
@@ -4189,7 +4189,7 @@
 3. Verify Validation response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:11.819Z</t>
+    <t>2026-07-25T16:00:18.436Z</t>
   </si>
   <si>
     <t>REG-APP-31</t>
@@ -4203,7 +4203,7 @@
 3. Verify Responsive response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:11.900Z</t>
+    <t>2026-07-25T16:00:18.474Z</t>
   </si>
   <si>
     <t>REG-APP-32</t>
@@ -4217,7 +4217,7 @@
 3. Verify Performance response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:11.982Z</t>
+    <t>2026-07-25T16:00:18.508Z</t>
   </si>
   <si>
     <t>REG-APP-33</t>
@@ -4231,7 +4231,7 @@
 3. Verify Security response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:12.054Z</t>
+    <t>2026-07-25T16:00:18.547Z</t>
   </si>
   <si>
     <t>REG-APP-34</t>
@@ -4245,7 +4245,7 @@
 3. Verify Accessibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:12.099Z</t>
+    <t>2026-07-25T16:00:18.582Z</t>
   </si>
   <si>
     <t>REG-APP-35</t>
@@ -4259,7 +4259,7 @@
 3. Verify UI Visibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:12.166Z</t>
+    <t>2026-07-25T16:00:18.619Z</t>
   </si>
   <si>
     <t>REG-APP-36</t>
@@ -4273,7 +4273,7 @@
 3. Verify Functional response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:12.230Z</t>
+    <t>2026-07-25T16:00:18.652Z</t>
   </si>
   <si>
     <t>FP-APP-06</t>
@@ -4290,7 +4290,7 @@
     <t>Mobile app behaves correctly for Accessibility capability #6</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:12.305Z</t>
+    <t>2026-07-25T16:00:18.690Z</t>
   </si>
   <si>
     <t>FP-APP-07</t>
@@ -4307,7 +4307,7 @@
     <t>Mobile app behaves correctly for UI Visibility capability #7</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:12.363Z</t>
+    <t>2026-07-25T16:00:18.723Z</t>
   </si>
   <si>
     <t>FP-APP-08</t>
@@ -4324,7 +4324,7 @@
     <t>Mobile app behaves correctly for Functional capability #8</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:12.440Z</t>
+    <t>2026-07-25T16:00:18.761Z</t>
   </si>
   <si>
     <t>FP-APP-09</t>
@@ -4341,7 +4341,7 @@
     <t>Mobile app behaves correctly for Validation capability #9</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:12.509Z</t>
+    <t>2026-07-25T16:00:18.800Z</t>
   </si>
   <si>
     <t>FP-APP-10</t>
@@ -4358,7 +4358,7 @@
     <t>Mobile app behaves correctly for Responsive capability #10</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:12.562Z</t>
+    <t>2026-07-25T16:00:18.840Z</t>
   </si>
   <si>
     <t>FP-APP-11</t>
@@ -4372,7 +4372,7 @@
 3. Verify Performance response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:12.621Z</t>
+    <t>2026-07-25T16:00:18.875Z</t>
   </si>
   <si>
     <t>FP-APP-12</t>
@@ -4386,7 +4386,7 @@
 3. Verify Security response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:12.681Z</t>
+    <t>2026-07-25T16:00:18.938Z</t>
   </si>
   <si>
     <t>FP-APP-13</t>
@@ -4400,7 +4400,7 @@
 3. Verify Accessibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:12.744Z</t>
+    <t>2026-07-25T16:00:19.007Z</t>
   </si>
   <si>
     <t>FP-APP-14</t>
@@ -4414,7 +4414,7 @@
 3. Verify UI Visibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:12.821Z</t>
+    <t>2026-07-25T16:00:19.063Z</t>
   </si>
   <si>
     <t>FP-APP-15</t>
@@ -4428,7 +4428,7 @@
 3. Verify Functional response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:12.870Z</t>
+    <t>2026-07-25T16:00:19.120Z</t>
   </si>
   <si>
     <t>FP-APP-16</t>
@@ -4442,7 +4442,7 @@
 3. Verify Validation response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:12.933Z</t>
+    <t>2026-07-25T16:00:19.160Z</t>
   </si>
   <si>
     <t>FP-APP-17</t>
@@ -4456,7 +4456,7 @@
 3. Verify Responsive response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:13.010Z</t>
+    <t>2026-07-25T16:00:19.196Z</t>
   </si>
   <si>
     <t>FP-APP-18</t>
@@ -4470,7 +4470,7 @@
 3. Verify Performance response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:13.082Z</t>
+    <t>2026-07-25T16:00:19.238Z</t>
   </si>
   <si>
     <t>FP-APP-19</t>
@@ -4484,7 +4484,7 @@
 3. Verify Security response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:13.150Z</t>
+    <t>2026-07-25T16:00:19.276Z</t>
   </si>
   <si>
     <t>FP-APP-20</t>
@@ -4498,7 +4498,7 @@
 3. Verify Accessibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:13.229Z</t>
+    <t>2026-07-25T16:00:19.317Z</t>
   </si>
   <si>
     <t>FP-APP-21</t>
@@ -4512,7 +4512,7 @@
 3. Verify UI Visibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:13.306Z</t>
+    <t>2026-07-25T16:00:19.358Z</t>
   </si>
   <si>
     <t>FP-APP-22</t>
@@ -4526,7 +4526,7 @@
 3. Verify Functional response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:13.381Z</t>
+    <t>2026-07-25T16:00:19.398Z</t>
   </si>
   <si>
     <t>FP-APP-23</t>
@@ -4540,7 +4540,7 @@
 3. Verify Validation response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:13.458Z</t>
+    <t>2026-07-25T16:00:19.442Z</t>
   </si>
   <si>
     <t>FP-APP-24</t>
@@ -4554,7 +4554,7 @@
 3. Verify Responsive response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:13.545Z</t>
+    <t>2026-07-25T16:00:19.482Z</t>
   </si>
   <si>
     <t>FP-APP-25</t>
@@ -4568,7 +4568,7 @@
 3. Verify Performance response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:13.627Z</t>
+    <t>2026-07-25T16:00:19.521Z</t>
   </si>
   <si>
     <t>FP-APP-26</t>
@@ -4582,7 +4582,7 @@
 3. Verify Security response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:13.718Z</t>
+    <t>2026-07-25T16:00:19.561Z</t>
   </si>
   <si>
     <t>FP-APP-27</t>
@@ -4596,7 +4596,7 @@
 3. Verify Accessibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:13.777Z</t>
+    <t>2026-07-25T16:00:19.605Z</t>
   </si>
   <si>
     <t>FP-APP-28</t>
@@ -4610,7 +4610,7 @@
 3. Verify UI Visibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:13.822Z</t>
+    <t>2026-07-25T16:00:19.646Z</t>
   </si>
   <si>
     <t>FP-APP-29</t>
@@ -4624,7 +4624,7 @@
 3. Verify Functional response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:13.873Z</t>
+    <t>2026-07-25T16:00:19.682Z</t>
   </si>
   <si>
     <t>FP-APP-30</t>
@@ -4638,7 +4638,7 @@
 3. Verify Validation response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:13.938Z</t>
+    <t>2026-07-25T16:00:19.718Z</t>
   </si>
   <si>
     <t>FP-APP-31</t>
@@ -4652,7 +4652,7 @@
 3. Verify Responsive response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:14.021Z</t>
+    <t>2026-07-25T16:00:19.754Z</t>
   </si>
   <si>
     <t>FP-APP-32</t>
@@ -4666,7 +4666,7 @@
 3. Verify Performance response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:14.111Z</t>
+    <t>2026-07-25T16:00:19.795Z</t>
   </si>
   <si>
     <t>FP-APP-33</t>
@@ -4680,7 +4680,7 @@
 3. Verify Security response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:14.168Z</t>
+    <t>2026-07-25T16:00:19.833Z</t>
   </si>
   <si>
     <t>FP-APP-34</t>
@@ -4694,7 +4694,7 @@
 3. Verify Accessibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:14.236Z</t>
+    <t>2026-07-25T16:00:19.882Z</t>
   </si>
   <si>
     <t>FP-APP-35</t>
@@ -4708,7 +4708,7 @@
 3. Verify UI Visibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:14.316Z</t>
+    <t>2026-07-25T16:00:19.926Z</t>
   </si>
   <si>
     <t>FP-APP-36</t>
@@ -4722,7 +4722,7 @@
 3. Verify Functional response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:14.410Z</t>
+    <t>2026-07-25T16:00:19.974Z</t>
   </si>
   <si>
     <t>DASH-APP-21</t>
@@ -4736,7 +4736,7 @@
 3. Verify UI Visibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:14.492Z</t>
+    <t>2026-07-25T16:00:20.014Z</t>
   </si>
   <si>
     <t>DASH-APP-22</t>
@@ -4750,7 +4750,7 @@
 3. Verify Functional response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:14.582Z</t>
+    <t>2026-07-25T16:00:20.055Z</t>
   </si>
   <si>
     <t>DASH-APP-23</t>
@@ -4764,7 +4764,7 @@
 3. Verify Validation response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:14.670Z</t>
+    <t>2026-07-25T16:00:20.091Z</t>
   </si>
   <si>
     <t>DASH-APP-24</t>
@@ -4778,7 +4778,7 @@
 3. Verify Responsive response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:14.751Z</t>
+    <t>2026-07-25T16:00:20.130Z</t>
   </si>
   <si>
     <t>DASH-APP-25</t>
@@ -4792,7 +4792,7 @@
 3. Verify Performance response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:14.831Z</t>
+    <t>2026-07-25T16:00:20.211Z</t>
   </si>
   <si>
     <t>DASH-APP-26</t>
@@ -4806,7 +4806,7 @@
 3. Verify Security response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:14.915Z</t>
+    <t>2026-07-25T16:00:20.278Z</t>
   </si>
   <si>
     <t>DASH-APP-27</t>
@@ -4820,7 +4820,7 @@
 3. Verify Accessibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:14.997Z</t>
+    <t>2026-07-25T16:00:20.321Z</t>
   </si>
   <si>
     <t>DASH-APP-28</t>
@@ -4834,7 +4834,7 @@
 3. Verify UI Visibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:15.081Z</t>
+    <t>2026-07-25T16:00:20.365Z</t>
   </si>
   <si>
     <t>DASH-APP-29</t>
@@ -4848,7 +4848,7 @@
 3. Verify Functional response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:15.157Z</t>
+    <t>2026-07-25T16:00:20.403Z</t>
   </si>
   <si>
     <t>DASH-APP-30</t>
@@ -4862,7 +4862,7 @@
 3. Verify Validation response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:15.264Z</t>
+    <t>2026-07-25T16:00:20.442Z</t>
   </si>
   <si>
     <t>DASH-APP-31</t>
@@ -4876,7 +4876,7 @@
 3. Verify Responsive response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:15.350Z</t>
+    <t>2026-07-25T16:00:20.484Z</t>
   </si>
   <si>
     <t>DASH-APP-32</t>
@@ -4890,7 +4890,7 @@
 3. Verify Performance response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:15.415Z</t>
+    <t>2026-07-25T16:00:20.531Z</t>
   </si>
   <si>
     <t>DASH-APP-33</t>
@@ -4904,7 +4904,7 @@
 3. Verify Security response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:15.492Z</t>
+    <t>2026-07-25T16:00:20.568Z</t>
   </si>
   <si>
     <t>DASH-APP-34</t>
@@ -4918,7 +4918,7 @@
 3. Verify Accessibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:15.582Z</t>
+    <t>2026-07-25T16:00:20.612Z</t>
   </si>
   <si>
     <t>DASH-APP-35</t>
@@ -4932,7 +4932,7 @@
 3. Verify UI Visibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:15.674Z</t>
+    <t>2026-07-25T16:00:20.651Z</t>
   </si>
   <si>
     <t>DASH-APP-36</t>
@@ -4946,7 +4946,7 @@
 3. Verify Functional response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:15.735Z</t>
+    <t>2026-07-25T16:00:20.688Z</t>
   </si>
   <si>
     <t>VOL-APP-23</t>
@@ -4960,7 +4960,7 @@
 3. Verify Validation response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:15.801Z</t>
+    <t>2026-07-25T16:00:20.728Z</t>
   </si>
   <si>
     <t>VOL-APP-24</t>
@@ -4974,7 +4974,7 @@
 3. Verify Responsive response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:15.890Z</t>
+    <t>2026-07-25T16:00:20.775Z</t>
   </si>
   <si>
     <t>VOL-APP-25</t>
@@ -4988,7 +4988,7 @@
 3. Verify Performance response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:15.969Z</t>
+    <t>2026-07-25T16:00:20.826Z</t>
   </si>
   <si>
     <t>VOL-APP-26</t>
@@ -5002,7 +5002,7 @@
 3. Verify Security response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:16.048Z</t>
+    <t>2026-07-25T16:00:20.869Z</t>
   </si>
   <si>
     <t>VOL-APP-27</t>
@@ -5016,7 +5016,7 @@
 3. Verify Accessibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:16.122Z</t>
+    <t>2026-07-25T16:00:20.911Z</t>
   </si>
   <si>
     <t>VOL-APP-28</t>
@@ -5030,7 +5030,7 @@
 3. Verify UI Visibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:16.212Z</t>
+    <t>2026-07-25T16:00:20.955Z</t>
   </si>
   <si>
     <t>VOL-APP-29</t>
@@ -5044,7 +5044,7 @@
 3. Verify Functional response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:16.304Z</t>
+    <t>2026-07-25T16:00:20.994Z</t>
   </si>
   <si>
     <t>VOL-APP-30</t>
@@ -5058,7 +5058,7 @@
 3. Verify Validation response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:16.387Z</t>
+    <t>2026-07-25T16:00:21.043Z</t>
   </si>
   <si>
     <t>VOL-APP-31</t>
@@ -5072,7 +5072,7 @@
 3. Verify Responsive response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:16.469Z</t>
+    <t>2026-07-25T16:00:21.085Z</t>
   </si>
   <si>
     <t>VOL-APP-32</t>
@@ -5086,7 +5086,7 @@
 3. Verify Performance response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:16.555Z</t>
+    <t>2026-07-25T16:00:21.130Z</t>
   </si>
   <si>
     <t>VOL-APP-33</t>
@@ -5100,7 +5100,7 @@
 3. Verify Security response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:16.632Z</t>
+    <t>2026-07-25T16:00:21.172Z</t>
   </si>
   <si>
     <t>VOL-APP-34</t>
@@ -5114,7 +5114,7 @@
 3. Verify Accessibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:16.725Z</t>
+    <t>2026-07-25T16:00:21.212Z</t>
   </si>
   <si>
     <t>VOL-APP-35</t>
@@ -5128,7 +5128,7 @@
 3. Verify UI Visibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:16.815Z</t>
+    <t>2026-07-25T16:00:21.253Z</t>
   </si>
   <si>
     <t>VOL-APP-36</t>
@@ -5142,7 +5142,7 @@
 3. Verify Functional response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:16.896Z</t>
+    <t>2026-07-25T16:00:21.299Z</t>
   </si>
   <si>
     <t>VOL-APP-37</t>
@@ -5159,7 +5159,7 @@
     <t>Mobile app behaves correctly for Validation capability #37</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:16.967Z</t>
+    <t>2026-07-25T16:00:21.344Z</t>
   </si>
   <si>
     <t>EVT-APP-25</t>
@@ -5173,7 +5173,7 @@
 3. Verify Performance response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:17.050Z</t>
+    <t>2026-07-25T16:00:21.385Z</t>
   </si>
   <si>
     <t>EVT-APP-26</t>
@@ -5187,7 +5187,7 @@
 3. Verify Security response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:17.141Z</t>
+    <t>2026-07-25T16:00:21.425Z</t>
   </si>
   <si>
     <t>EVT-APP-27</t>
@@ -5201,7 +5201,7 @@
 3. Verify Accessibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:17.231Z</t>
+    <t>2026-07-25T16:00:21.472Z</t>
   </si>
   <si>
     <t>EVT-APP-28</t>
@@ -5215,7 +5215,7 @@
 3. Verify UI Visibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:17.322Z</t>
+    <t>2026-07-25T16:00:21.514Z</t>
   </si>
   <si>
     <t>EVT-APP-29</t>
@@ -5229,7 +5229,7 @@
 3. Verify Functional response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:17.419Z</t>
+    <t>2026-07-25T16:00:21.558Z</t>
   </si>
   <si>
     <t>EVT-APP-30</t>
@@ -5243,7 +5243,7 @@
 3. Verify Validation response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:17.507Z</t>
+    <t>2026-07-25T16:00:21.596Z</t>
   </si>
   <si>
     <t>EVT-APP-31</t>
@@ -5257,7 +5257,7 @@
 3. Verify Responsive response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:17.611Z</t>
+    <t>2026-07-25T16:00:21.649Z</t>
   </si>
   <si>
     <t>EVT-APP-32</t>
@@ -5271,7 +5271,7 @@
 3. Verify Performance response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:17.681Z</t>
+    <t>2026-07-25T16:00:21.689Z</t>
   </si>
   <si>
     <t>EVT-APP-33</t>
@@ -5285,7 +5285,7 @@
 3. Verify Security response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:17.751Z</t>
+    <t>2026-07-25T16:00:21.734Z</t>
   </si>
   <si>
     <t>EVT-APP-34</t>
@@ -5299,7 +5299,7 @@
 3. Verify Accessibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:17.803Z</t>
+    <t>2026-07-25T16:00:21.779Z</t>
   </si>
   <si>
     <t>EVT-APP-35</t>
@@ -5313,7 +5313,7 @@
 3. Verify UI Visibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:17.853Z</t>
+    <t>2026-07-25T16:00:21.827Z</t>
   </si>
   <si>
     <t>EVT-APP-36</t>
@@ -5327,7 +5327,7 @@
 3. Verify Functional response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:17.909Z</t>
+    <t>2026-07-25T16:00:21.870Z</t>
   </si>
   <si>
     <t>EVT-APP-37</t>
@@ -5341,7 +5341,7 @@
 3. Verify Validation response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:17.987Z</t>
+    <t>2026-07-25T16:00:21.918Z</t>
   </si>
   <si>
     <t>ATT-APP-26</t>
@@ -5355,7 +5355,7 @@
 3. Verify Security response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:18.061Z</t>
+    <t>2026-07-25T16:00:21.959Z</t>
   </si>
   <si>
     <t>ATT-APP-27</t>
@@ -5369,7 +5369,7 @@
 3. Verify Accessibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:18.129Z</t>
+    <t>2026-07-25T16:00:22.002Z</t>
   </si>
   <si>
     <t>ATT-APP-28</t>
@@ -5383,7 +5383,7 @@
 3. Verify UI Visibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:18.198Z</t>
+    <t>2026-07-25T16:00:22.045Z</t>
   </si>
   <si>
     <t>ATT-APP-29</t>
@@ -5397,7 +5397,7 @@
 3. Verify Functional response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:18.267Z</t>
+    <t>2026-07-25T16:00:22.087Z</t>
   </si>
   <si>
     <t>ATT-APP-30</t>
@@ -5411,7 +5411,7 @@
 3. Verify Validation response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:18.330Z</t>
+    <t>2026-07-25T16:00:22.138Z</t>
   </si>
   <si>
     <t>ATT-APP-31</t>
@@ -5425,7 +5425,7 @@
 3. Verify Responsive response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:18.408Z</t>
+    <t>2026-07-25T16:00:22.187Z</t>
   </si>
   <si>
     <t>ATT-APP-32</t>
@@ -5439,7 +5439,7 @@
 3. Verify Performance response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:18.477Z</t>
+    <t>2026-07-25T16:00:22.233Z</t>
   </si>
   <si>
     <t>ATT-APP-33</t>
@@ -5453,7 +5453,7 @@
 3. Verify Security response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:18.548Z</t>
+    <t>2026-07-25T16:00:22.276Z</t>
   </si>
   <si>
     <t>ATT-APP-34</t>
@@ -5467,7 +5467,7 @@
 3. Verify Accessibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:18.616Z</t>
+    <t>2026-07-25T16:00:22.320Z</t>
   </si>
   <si>
     <t>ATT-APP-35</t>
@@ -5481,7 +5481,7 @@
 3. Verify UI Visibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:18.688Z</t>
+    <t>2026-07-25T16:00:22.362Z</t>
   </si>
   <si>
     <t>ATT-APP-36</t>
@@ -5495,7 +5495,7 @@
 3. Verify Functional response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:18.771Z</t>
+    <t>2026-07-25T16:00:22.405Z</t>
   </si>
   <si>
     <t>ATT-APP-37</t>
@@ -5509,7 +5509,7 @@
 3. Verify Validation response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:18.841Z</t>
+    <t>2026-07-25T16:00:22.451Z</t>
   </si>
   <si>
     <t>REP-APP-16</t>
@@ -5523,7 +5523,7 @@
 3. Verify Validation response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:18.912Z</t>
+    <t>2026-07-25T16:00:22.492Z</t>
   </si>
   <si>
     <t>REP-APP-17</t>
@@ -5537,7 +5537,7 @@
 3. Verify Responsive response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:18.969Z</t>
+    <t>2026-07-25T16:00:22.539Z</t>
   </si>
   <si>
     <t>REP-APP-18</t>
@@ -5551,7 +5551,7 @@
 3. Verify Performance response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:19.020Z</t>
+    <t>2026-07-25T16:00:22.585Z</t>
   </si>
   <si>
     <t>REP-APP-19</t>
@@ -5565,7 +5565,7 @@
 3. Verify Security response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:19.106Z</t>
+    <t>2026-07-25T16:00:22.635Z</t>
   </si>
   <si>
     <t>REP-APP-20</t>
@@ -5579,7 +5579,7 @@
 3. Verify Accessibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:19.177Z</t>
+    <t>2026-07-25T16:00:22.678Z</t>
   </si>
   <si>
     <t>REP-APP-21</t>
@@ -5593,7 +5593,7 @@
 3. Verify UI Visibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:19.264Z</t>
+    <t>2026-07-25T16:00:22.720Z</t>
   </si>
   <si>
     <t>REP-APP-22</t>
@@ -5607,7 +5607,7 @@
 3. Verify Functional response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:19.324Z</t>
+    <t>2026-07-25T16:00:22.761Z</t>
   </si>
   <si>
     <t>REP-APP-23</t>
@@ -5621,7 +5621,7 @@
 3. Verify Validation response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:19.411Z</t>
+    <t>2026-07-25T16:00:22.810Z</t>
   </si>
   <si>
     <t>REP-APP-24</t>
@@ -5635,7 +5635,7 @@
 3. Verify Responsive response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:19.497Z</t>
+    <t>2026-07-25T16:00:22.854Z</t>
   </si>
   <si>
     <t>REP-APP-25</t>
@@ -5649,7 +5649,7 @@
 3. Verify Performance response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:19.566Z</t>
+    <t>2026-07-25T16:00:22.905Z</t>
   </si>
   <si>
     <t>REP-APP-26</t>
@@ -5663,7 +5663,7 @@
 3. Verify Security response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:19.632Z</t>
+    <t>2026-07-25T16:00:22.948Z</t>
   </si>
   <si>
     <t>REP-APP-27</t>
@@ -5677,7 +5677,7 @@
 3. Verify Accessibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:19.716Z</t>
+    <t>2026-07-25T16:00:22.995Z</t>
   </si>
   <si>
     <t>REP-APP-28</t>
@@ -5691,7 +5691,7 @@
 3. Verify UI Visibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:19.789Z</t>
+    <t>2026-07-25T16:00:23.041Z</t>
   </si>
   <si>
     <t>REP-APP-29</t>
@@ -5705,7 +5705,7 @@
 3. Verify Functional response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:19.922Z</t>
+    <t>2026-07-25T16:00:23.090Z</t>
   </si>
   <si>
     <t>REP-APP-30</t>
@@ -5719,7 +5719,7 @@
 3. Verify Validation response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:19.985Z</t>
+    <t>2026-07-25T16:00:23.133Z</t>
   </si>
   <si>
     <t>REP-APP-31</t>
@@ -5733,7 +5733,7 @@
 3. Verify Responsive response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:20.055Z</t>
+    <t>2026-07-25T16:00:23.177Z</t>
   </si>
   <si>
     <t>REP-APP-32</t>
@@ -5747,7 +5747,7 @@
 3. Verify Performance response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:20.123Z</t>
+    <t>2026-07-25T16:00:23.221Z</t>
   </si>
   <si>
     <t>REP-APP-33</t>
@@ -5761,7 +5761,7 @@
 3. Verify Security response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:20.197Z</t>
+    <t>2026-07-25T16:00:23.278Z</t>
   </si>
   <si>
     <t>REP-APP-34</t>
@@ -5775,7 +5775,7 @@
 3. Verify Accessibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:20.277Z</t>
+    <t>2026-07-25T16:00:23.327Z</t>
   </si>
   <si>
     <t>REP-APP-35</t>
@@ -5789,7 +5789,7 @@
 3. Verify UI Visibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:20.343Z</t>
+    <t>2026-07-25T16:00:23.376Z</t>
   </si>
   <si>
     <t>REP-APP-36</t>
@@ -5803,7 +5803,7 @@
 3. Verify Functional response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:20.408Z</t>
+    <t>2026-07-25T16:00:23.418Z</t>
   </si>
   <si>
     <t>REP-APP-37</t>
@@ -5817,7 +5817,7 @@
 3. Verify Validation response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:20.482Z</t>
+    <t>2026-07-25T16:00:23.471Z</t>
   </si>
   <si>
     <t>SET-APP-24</t>
@@ -5831,7 +5831,7 @@
 3. Verify Responsive response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:20.542Z</t>
+    <t>2026-07-25T16:00:23.516Z</t>
   </si>
   <si>
     <t>SET-APP-25</t>
@@ -5845,7 +5845,7 @@
 3. Verify Performance response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:20.614Z</t>
+    <t>2026-07-25T16:00:23.564Z</t>
   </si>
   <si>
     <t>SET-APP-26</t>
@@ -5859,7 +5859,7 @@
 3. Verify Security response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:20.685Z</t>
+    <t>2026-07-25T16:00:23.609Z</t>
   </si>
   <si>
     <t>SET-APP-27</t>
@@ -5873,7 +5873,7 @@
 3. Verify Accessibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:20.757Z</t>
+    <t>2026-07-25T16:00:23.662Z</t>
   </si>
   <si>
     <t>SET-APP-28</t>
@@ -5887,7 +5887,7 @@
 3. Verify UI Visibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:20.815Z</t>
+    <t>2026-07-25T16:00:23.710Z</t>
   </si>
   <si>
     <t>SET-APP-29</t>
@@ -5901,7 +5901,7 @@
 3. Verify Functional response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:20.879Z</t>
+    <t>2026-07-25T16:00:23.759Z</t>
   </si>
   <si>
     <t>SET-APP-30</t>
@@ -5915,7 +5915,7 @@
 3. Verify Validation response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:20.937Z</t>
+    <t>2026-07-25T16:00:23.805Z</t>
   </si>
   <si>
     <t>SET-APP-31</t>
@@ -5929,7 +5929,7 @@
 3. Verify Responsive response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:21.016Z</t>
+    <t>2026-07-25T16:00:23.853Z</t>
   </si>
   <si>
     <t>SET-APP-32</t>
@@ -5943,7 +5943,7 @@
 3. Verify Performance response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:21.070Z</t>
+    <t>2026-07-25T16:00:23.899Z</t>
   </si>
   <si>
     <t>SET-APP-33</t>
@@ -5957,7 +5957,7 @@
 3. Verify Security response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:21.137Z</t>
+    <t>2026-07-25T16:00:23.970Z</t>
   </si>
   <si>
     <t>SET-APP-34</t>
@@ -5971,7 +5971,7 @@
 3. Verify Accessibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:21.218Z</t>
+    <t>2026-07-25T16:00:24.027Z</t>
   </si>
   <si>
     <t>SET-APP-35</t>
@@ -5985,7 +5985,7 @@
 3. Verify UI Visibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:21.294Z</t>
+    <t>2026-07-25T16:00:24.080Z</t>
   </si>
   <si>
     <t>SET-APP-36</t>
@@ -5999,7 +5999,7 @@
 3. Verify Functional response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:21.372Z</t>
+    <t>2026-07-25T16:00:24.132Z</t>
   </si>
   <si>
     <t>SET-APP-37</t>
@@ -6013,7 +6013,7 @@
 3. Verify Validation response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:21.442Z</t>
+    <t>2026-07-25T16:00:24.185Z</t>
   </si>
   <si>
     <t>AI-APP-16</t>
@@ -6027,7 +6027,7 @@
 3. Verify Validation response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:21.505Z</t>
+    <t>2026-07-25T16:00:24.236Z</t>
   </si>
   <si>
     <t>AI-APP-17</t>
@@ -6041,7 +6041,7 @@
 3. Verify Responsive response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:21.568Z</t>
+    <t>2026-07-25T16:00:24.286Z</t>
   </si>
   <si>
     <t>AI-APP-18</t>
@@ -6055,7 +6055,7 @@
 3. Verify Performance response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:21.662Z</t>
+    <t>2026-07-25T16:00:24.339Z</t>
   </si>
   <si>
     <t>AI-APP-19</t>
@@ -6069,7 +6069,7 @@
 3. Verify Security response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:21.742Z</t>
+    <t>2026-07-25T16:00:24.393Z</t>
   </si>
   <si>
     <t>AI-APP-20</t>
@@ -6083,7 +6083,7 @@
 3. Verify Accessibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:21.825Z</t>
+    <t>2026-07-25T16:00:24.443Z</t>
   </si>
   <si>
     <t>AI-APP-21</t>
@@ -6097,7 +6097,7 @@
 3. Verify UI Visibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:21.889Z</t>
+    <t>2026-07-25T16:00:24.493Z</t>
   </si>
   <si>
     <t>AI-APP-22</t>
@@ -6111,7 +6111,7 @@
 3. Verify Functional response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:21.962Z</t>
+    <t>2026-07-25T16:00:24.543Z</t>
   </si>
   <si>
     <t>AI-APP-23</t>
@@ -6125,7 +6125,7 @@
 3. Verify Validation response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:22.079Z</t>
+    <t>2026-07-25T16:00:24.591Z</t>
   </si>
   <si>
     <t>AI-APP-24</t>
@@ -6139,7 +6139,7 @@
 3. Verify Responsive response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:22.168Z</t>
+    <t>2026-07-25T16:00:24.640Z</t>
   </si>
   <si>
     <t>AI-APP-25</t>
@@ -6153,7 +6153,7 @@
 3. Verify Performance response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:22.247Z</t>
+    <t>2026-07-25T16:00:24.686Z</t>
   </si>
   <si>
     <t>AI-APP-26</t>
@@ -6167,7 +6167,7 @@
 3. Verify Security response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:22.325Z</t>
+    <t>2026-07-25T16:00:24.732Z</t>
   </si>
   <si>
     <t>AI-APP-27</t>
@@ -6181,7 +6181,7 @@
 3. Verify Accessibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:22.407Z</t>
+    <t>2026-07-25T16:00:24.783Z</t>
   </si>
   <si>
     <t>AI-APP-28</t>
@@ -6195,7 +6195,7 @@
 3. Verify UI Visibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:22.489Z</t>
+    <t>2026-07-25T16:00:24.830Z</t>
   </si>
   <si>
     <t>AI-APP-29</t>
@@ -6209,7 +6209,7 @@
 3. Verify Functional response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:22.572Z</t>
+    <t>2026-07-25T16:00:24.912Z</t>
   </si>
   <si>
     <t>AI-APP-30</t>
@@ -6223,7 +6223,7 @@
 3. Verify Validation response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:22.675Z</t>
+    <t>2026-07-25T16:00:24.958Z</t>
   </si>
   <si>
     <t>AI-APP-31</t>
@@ -6237,7 +6237,7 @@
 3. Verify Responsive response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:22.770Z</t>
+    <t>2026-07-25T16:00:25.008Z</t>
   </si>
   <si>
     <t>AI-APP-32</t>
@@ -6251,7 +6251,7 @@
 3. Verify Performance response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:22.854Z</t>
+    <t>2026-07-25T16:00:25.062Z</t>
   </si>
   <si>
     <t>AI-APP-33</t>
@@ -6265,7 +6265,7 @@
 3. Verify Security response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:22.932Z</t>
+    <t>2026-07-25T16:00:25.110Z</t>
   </si>
   <si>
     <t>AI-APP-34</t>
@@ -6279,7 +6279,7 @@
 3. Verify Accessibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:23.019Z</t>
+    <t>2026-07-25T16:00:25.163Z</t>
   </si>
   <si>
     <t>AI-APP-35</t>
@@ -6293,7 +6293,7 @@
 3. Verify UI Visibility response on Mobile.</t>
   </si>
   <si>
-    <t>2026-07-23T04:51:23.091Z</t>
+    <t>2026-07-25T16:00:25.207Z</t>
   </si>
 </sst>
 </file>
@@ -7141,7 +7141,7 @@
         <v>6</v>
       </c>
       <c r="J2" s="4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>42</v>
@@ -7179,7 +7179,7 @@
         <v>6</v>
       </c>
       <c r="J3" s="4">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>49</v>
@@ -7217,7 +7217,7 @@
         <v>6</v>
       </c>
       <c r="J4" s="4">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>55</v>
@@ -7255,7 +7255,7 @@
         <v>6</v>
       </c>
       <c r="J5" s="4">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>60</v>
@@ -7293,7 +7293,7 @@
         <v>6</v>
       </c>
       <c r="J6" s="4">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>65</v>
@@ -7331,7 +7331,7 @@
         <v>6</v>
       </c>
       <c r="J7" s="4">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>71</v>
@@ -7369,7 +7369,7 @@
         <v>6</v>
       </c>
       <c r="J8" s="4">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>77</v>
@@ -7407,7 +7407,7 @@
         <v>6</v>
       </c>
       <c r="J9" s="4">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>82</v>
@@ -7445,7 +7445,7 @@
         <v>6</v>
       </c>
       <c r="J10" s="4">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>87</v>
@@ -7483,7 +7483,7 @@
         <v>6</v>
       </c>
       <c r="J11" s="4">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>92</v>
@@ -7521,7 +7521,7 @@
         <v>6</v>
       </c>
       <c r="J12" s="4">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>97</v>
@@ -7559,7 +7559,7 @@
         <v>6</v>
       </c>
       <c r="J13" s="4">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>103</v>
@@ -7597,7 +7597,7 @@
         <v>6</v>
       </c>
       <c r="J14" s="4">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>108</v>
@@ -7635,7 +7635,7 @@
         <v>6</v>
       </c>
       <c r="J15" s="4">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>113</v>
@@ -7673,7 +7673,7 @@
         <v>6</v>
       </c>
       <c r="J16" s="4">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>118</v>
@@ -7711,7 +7711,7 @@
         <v>6</v>
       </c>
       <c r="J17" s="4">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>123</v>
@@ -7749,7 +7749,7 @@
         <v>6</v>
       </c>
       <c r="J18" s="4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>129</v>
@@ -7787,7 +7787,7 @@
         <v>6</v>
       </c>
       <c r="J19" s="4">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K19" s="4" t="s">
         <v>134</v>
@@ -7825,7 +7825,7 @@
         <v>6</v>
       </c>
       <c r="J20" s="4">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>139</v>
@@ -7863,7 +7863,7 @@
         <v>6</v>
       </c>
       <c r="J21" s="4">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>144</v>
@@ -7901,7 +7901,7 @@
         <v>6</v>
       </c>
       <c r="J22" s="4">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>150</v>
@@ -7939,7 +7939,7 @@
         <v>6</v>
       </c>
       <c r="J23" s="4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K23" s="4" t="s">
         <v>155</v>
@@ -7977,7 +7977,7 @@
         <v>6</v>
       </c>
       <c r="J24" s="4">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K24" s="4" t="s">
         <v>160</v>
@@ -8015,7 +8015,7 @@
         <v>6</v>
       </c>
       <c r="J25" s="4">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K25" s="4" t="s">
         <v>164</v>
@@ -8053,7 +8053,7 @@
         <v>6</v>
       </c>
       <c r="J26" s="4">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K26" s="4" t="s">
         <v>169</v>
@@ -8091,7 +8091,7 @@
         <v>6</v>
       </c>
       <c r="J27" s="4">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>174</v>
@@ -8205,7 +8205,7 @@
         <v>6</v>
       </c>
       <c r="J30" s="4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K30" s="4" t="s">
         <v>189</v>
@@ -8281,7 +8281,7 @@
         <v>6</v>
       </c>
       <c r="J32" s="4">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>199</v>
@@ -8319,7 +8319,7 @@
         <v>6</v>
       </c>
       <c r="J33" s="4">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K33" s="4" t="s">
         <v>204</v>
@@ -8357,7 +8357,7 @@
         <v>6</v>
       </c>
       <c r="J34" s="4">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K34" s="4" t="s">
         <v>209</v>
@@ -8395,7 +8395,7 @@
         <v>6</v>
       </c>
       <c r="J35" s="4">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="K35" s="4" t="s">
         <v>214</v>
@@ -8433,7 +8433,7 @@
         <v>6</v>
       </c>
       <c r="J36" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K36" s="4" t="s">
         <v>219</v>
@@ -8471,7 +8471,7 @@
         <v>6</v>
       </c>
       <c r="J37" s="4">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K37" s="4" t="s">
         <v>224</v>
@@ -8509,7 +8509,7 @@
         <v>6</v>
       </c>
       <c r="J38" s="4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K38" s="4" t="s">
         <v>227</v>
@@ -8547,7 +8547,7 @@
         <v>6</v>
       </c>
       <c r="J39" s="4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K39" s="4" t="s">
         <v>232</v>
@@ -8623,7 +8623,7 @@
         <v>6</v>
       </c>
       <c r="J41" s="4">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K41" s="4" t="s">
         <v>243</v>
@@ -8661,7 +8661,7 @@
         <v>6</v>
       </c>
       <c r="J42" s="4">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K42" s="4" t="s">
         <v>248</v>
@@ -8699,7 +8699,7 @@
         <v>6</v>
       </c>
       <c r="J43" s="4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K43" s="4" t="s">
         <v>253</v>
@@ -8813,7 +8813,7 @@
         <v>6</v>
       </c>
       <c r="J46" s="4">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K46" s="4" t="s">
         <v>268</v>
@@ -8851,7 +8851,7 @@
         <v>6</v>
       </c>
       <c r="J47" s="4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K47" s="4" t="s">
         <v>273</v>
@@ -8889,7 +8889,7 @@
         <v>6</v>
       </c>
       <c r="J48" s="4">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K48" s="4" t="s">
         <v>278</v>
@@ -8927,7 +8927,7 @@
         <v>6</v>
       </c>
       <c r="J49" s="4">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="K49" s="4" t="s">
         <v>283</v>
@@ -8965,7 +8965,7 @@
         <v>6</v>
       </c>
       <c r="J50" s="4">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K50" s="4" t="s">
         <v>288</v>
@@ -9003,7 +9003,7 @@
         <v>6</v>
       </c>
       <c r="J51" s="4">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K51" s="4" t="s">
         <v>293</v>
@@ -9041,7 +9041,7 @@
         <v>6</v>
       </c>
       <c r="J52" s="4">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K52" s="4" t="s">
         <v>298</v>
@@ -9079,7 +9079,7 @@
         <v>6</v>
       </c>
       <c r="J53" s="4">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K53" s="4" t="s">
         <v>303</v>
@@ -9117,7 +9117,7 @@
         <v>6</v>
       </c>
       <c r="J54" s="4">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K54" s="4" t="s">
         <v>308</v>
@@ -9155,7 +9155,7 @@
         <v>6</v>
       </c>
       <c r="J55" s="4">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K55" s="4" t="s">
         <v>313</v>
@@ -9193,7 +9193,7 @@
         <v>6</v>
       </c>
       <c r="J56" s="4">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K56" s="4" t="s">
         <v>318</v>
@@ -9231,7 +9231,7 @@
         <v>6</v>
       </c>
       <c r="J57" s="4">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K57" s="4" t="s">
         <v>323</v>
@@ -9269,7 +9269,7 @@
         <v>6</v>
       </c>
       <c r="J58" s="4">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K58" s="4" t="s">
         <v>328</v>
@@ -9307,7 +9307,7 @@
         <v>6</v>
       </c>
       <c r="J59" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K59" s="4" t="s">
         <v>333</v>
@@ -9345,7 +9345,7 @@
         <v>6</v>
       </c>
       <c r="J60" s="4">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K60" s="4" t="s">
         <v>338</v>
@@ -9383,7 +9383,7 @@
         <v>6</v>
       </c>
       <c r="J61" s="4">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K61" s="4" t="s">
         <v>343</v>
@@ -9421,7 +9421,7 @@
         <v>6</v>
       </c>
       <c r="J62" s="4">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K62" s="4" t="s">
         <v>348</v>
@@ -9459,7 +9459,7 @@
         <v>6</v>
       </c>
       <c r="J63" s="4">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K63" s="4" t="s">
         <v>353</v>
@@ -9497,7 +9497,7 @@
         <v>6</v>
       </c>
       <c r="J64" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K64" s="4" t="s">
         <v>358</v>
@@ -9535,7 +9535,7 @@
         <v>6</v>
       </c>
       <c r="J65" s="4">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K65" s="4" t="s">
         <v>363</v>
@@ -9573,7 +9573,7 @@
         <v>6</v>
       </c>
       <c r="J66" s="4">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K66" s="4" t="s">
         <v>368</v>
@@ -9611,7 +9611,7 @@
         <v>6</v>
       </c>
       <c r="J67" s="4">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="K67" s="4" t="s">
         <v>373</v>
@@ -9649,7 +9649,7 @@
         <v>6</v>
       </c>
       <c r="J68" s="4">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K68" s="4" t="s">
         <v>378</v>
@@ -9687,7 +9687,7 @@
         <v>6</v>
       </c>
       <c r="J69" s="4">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K69" s="4" t="s">
         <v>383</v>
@@ -9725,7 +9725,7 @@
         <v>6</v>
       </c>
       <c r="J70" s="4">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K70" s="4" t="s">
         <v>388</v>
@@ -9763,7 +9763,7 @@
         <v>6</v>
       </c>
       <c r="J71" s="4">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K71" s="4" t="s">
         <v>393</v>
@@ -9801,7 +9801,7 @@
         <v>6</v>
       </c>
       <c r="J72" s="4">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K72" s="4" t="s">
         <v>398</v>
@@ -9839,7 +9839,7 @@
         <v>6</v>
       </c>
       <c r="J73" s="4">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K73" s="4" t="s">
         <v>403</v>
@@ -9877,7 +9877,7 @@
         <v>6</v>
       </c>
       <c r="J74" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K74" s="4" t="s">
         <v>408</v>
@@ -9915,7 +9915,7 @@
         <v>6</v>
       </c>
       <c r="J75" s="4">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K75" s="4" t="s">
         <v>413</v>
@@ -9953,7 +9953,7 @@
         <v>6</v>
       </c>
       <c r="J76" s="4">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K76" s="4" t="s">
         <v>418</v>
@@ -9991,7 +9991,7 @@
         <v>6</v>
       </c>
       <c r="J77" s="4">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="K77" s="4" t="s">
         <v>423</v>
@@ -10029,7 +10029,7 @@
         <v>6</v>
       </c>
       <c r="J78" s="4">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K78" s="4" t="s">
         <v>428</v>
@@ -10067,7 +10067,7 @@
         <v>6</v>
       </c>
       <c r="J79" s="4">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K79" s="4" t="s">
         <v>433</v>
@@ -10105,7 +10105,7 @@
         <v>6</v>
       </c>
       <c r="J80" s="4">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K80" s="4" t="s">
         <v>438</v>
@@ -10143,7 +10143,7 @@
         <v>6</v>
       </c>
       <c r="J81" s="4">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="K81" s="4" t="s">
         <v>443</v>
@@ -10181,7 +10181,7 @@
         <v>6</v>
       </c>
       <c r="J82" s="4">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K82" s="4" t="s">
         <v>448</v>
@@ -10219,7 +10219,7 @@
         <v>6</v>
       </c>
       <c r="J83" s="4">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K83" s="4" t="s">
         <v>453</v>
@@ -10257,7 +10257,7 @@
         <v>6</v>
       </c>
       <c r="J84" s="4">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="K84" s="4" t="s">
         <v>458</v>
@@ -10295,7 +10295,7 @@
         <v>6</v>
       </c>
       <c r="J85" s="4">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="K85" s="4" t="s">
         <v>463</v>
@@ -10333,7 +10333,7 @@
         <v>6</v>
       </c>
       <c r="J86" s="4">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="K86" s="4" t="s">
         <v>468</v>
@@ -10371,7 +10371,7 @@
         <v>6</v>
       </c>
       <c r="J87" s="4">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K87" s="4" t="s">
         <v>473</v>
@@ -10409,7 +10409,7 @@
         <v>6</v>
       </c>
       <c r="J88" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K88" s="4" t="s">
         <v>478</v>
@@ -10447,7 +10447,7 @@
         <v>6</v>
       </c>
       <c r="J89" s="4">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K89" s="4" t="s">
         <v>483</v>
@@ -10485,7 +10485,7 @@
         <v>6</v>
       </c>
       <c r="J90" s="4">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K90" s="4" t="s">
         <v>488</v>
@@ -10523,7 +10523,7 @@
         <v>6</v>
       </c>
       <c r="J91" s="4">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K91" s="4" t="s">
         <v>493</v>
@@ -10561,7 +10561,7 @@
         <v>6</v>
       </c>
       <c r="J92" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K92" s="4" t="s">
         <v>498</v>
@@ -10599,7 +10599,7 @@
         <v>6</v>
       </c>
       <c r="J93" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K93" s="4" t="s">
         <v>503</v>
@@ -10637,7 +10637,7 @@
         <v>6</v>
       </c>
       <c r="J94" s="4">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K94" s="4" t="s">
         <v>508</v>
@@ -10713,7 +10713,7 @@
         <v>6</v>
       </c>
       <c r="J96" s="4">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="K96" s="4" t="s">
         <v>518</v>
@@ -10751,7 +10751,7 @@
         <v>6</v>
       </c>
       <c r="J97" s="4">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K97" s="4" t="s">
         <v>523</v>
@@ -10789,7 +10789,7 @@
         <v>6</v>
       </c>
       <c r="J98" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K98" s="4" t="s">
         <v>528</v>
@@ -10827,7 +10827,7 @@
         <v>6</v>
       </c>
       <c r="J99" s="4">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K99" s="4" t="s">
         <v>533</v>
@@ -10865,7 +10865,7 @@
         <v>6</v>
       </c>
       <c r="J100" s="4">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K100" s="4" t="s">
         <v>538</v>
@@ -10903,7 +10903,7 @@
         <v>6</v>
       </c>
       <c r="J101" s="4">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K101" s="4" t="s">
         <v>543</v>
@@ -10941,7 +10941,7 @@
         <v>6</v>
       </c>
       <c r="J102" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K102" s="4" t="s">
         <v>548</v>
@@ -10979,7 +10979,7 @@
         <v>6</v>
       </c>
       <c r="J103" s="4">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K103" s="4" t="s">
         <v>553</v>
@@ -11017,7 +11017,7 @@
         <v>6</v>
       </c>
       <c r="J104" s="4">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="K104" s="4" t="s">
         <v>558</v>
@@ -11055,7 +11055,7 @@
         <v>6</v>
       </c>
       <c r="J105" s="4">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K105" s="4" t="s">
         <v>563</v>
@@ -11093,7 +11093,7 @@
         <v>6</v>
       </c>
       <c r="J106" s="4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K106" s="4" t="s">
         <v>568</v>
@@ -11131,7 +11131,7 @@
         <v>6</v>
       </c>
       <c r="J107" s="4">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K107" s="4" t="s">
         <v>573</v>
@@ -11169,7 +11169,7 @@
         <v>6</v>
       </c>
       <c r="J108" s="4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K108" s="4" t="s">
         <v>578</v>
@@ -11207,7 +11207,7 @@
         <v>6</v>
       </c>
       <c r="J109" s="4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K109" s="4" t="s">
         <v>583</v>
@@ -11245,7 +11245,7 @@
         <v>6</v>
       </c>
       <c r="J110" s="4">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K110" s="4" t="s">
         <v>588</v>
@@ -11283,7 +11283,7 @@
         <v>6</v>
       </c>
       <c r="J111" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K111" s="4" t="s">
         <v>593</v>
@@ -11321,7 +11321,7 @@
         <v>6</v>
       </c>
       <c r="J112" s="4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K112" s="4" t="s">
         <v>598</v>
@@ -11359,7 +11359,7 @@
         <v>6</v>
       </c>
       <c r="J113" s="4">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K113" s="4" t="s">
         <v>603</v>
@@ -11397,7 +11397,7 @@
         <v>6</v>
       </c>
       <c r="J114" s="4">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="K114" s="4" t="s">
         <v>608</v>
@@ -11435,7 +11435,7 @@
         <v>6</v>
       </c>
       <c r="J115" s="4">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K115" s="4" t="s">
         <v>613</v>
@@ -11473,7 +11473,7 @@
         <v>6</v>
       </c>
       <c r="J116" s="4">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K116" s="4" t="s">
         <v>618</v>
@@ -11511,7 +11511,7 @@
         <v>6</v>
       </c>
       <c r="J117" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K117" s="4" t="s">
         <v>623</v>
@@ -11549,7 +11549,7 @@
         <v>6</v>
       </c>
       <c r="J118" s="4">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="K118" s="4" t="s">
         <v>628</v>
@@ -11587,7 +11587,7 @@
         <v>6</v>
       </c>
       <c r="J119" s="4">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K119" s="4" t="s">
         <v>633</v>
@@ -11625,7 +11625,7 @@
         <v>6</v>
       </c>
       <c r="J120" s="4">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="K120" s="4" t="s">
         <v>638</v>
@@ -11663,7 +11663,7 @@
         <v>6</v>
       </c>
       <c r="J121" s="4">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="K121" s="4" t="s">
         <v>643</v>
@@ -11701,7 +11701,7 @@
         <v>6</v>
       </c>
       <c r="J122" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K122" s="4" t="s">
         <v>648</v>
@@ -11739,7 +11739,7 @@
         <v>6</v>
       </c>
       <c r="J123" s="4">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="K123" s="4" t="s">
         <v>653</v>
@@ -11777,7 +11777,7 @@
         <v>6</v>
       </c>
       <c r="J124" s="4">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="K124" s="4" t="s">
         <v>658</v>
@@ -11815,7 +11815,7 @@
         <v>6</v>
       </c>
       <c r="J125" s="4">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="K125" s="4" t="s">
         <v>663</v>
@@ -11853,7 +11853,7 @@
         <v>6</v>
       </c>
       <c r="J126" s="4">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="K126" s="4" t="s">
         <v>668</v>
@@ -11891,7 +11891,7 @@
         <v>6</v>
       </c>
       <c r="J127" s="4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K127" s="4" t="s">
         <v>673</v>
@@ -11929,7 +11929,7 @@
         <v>6</v>
       </c>
       <c r="J128" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K128" s="4" t="s">
         <v>678</v>
@@ -11967,7 +11967,7 @@
         <v>6</v>
       </c>
       <c r="J129" s="4">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K129" s="4" t="s">
         <v>683</v>
@@ -12005,7 +12005,7 @@
         <v>6</v>
       </c>
       <c r="J130" s="4">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="K130" s="4" t="s">
         <v>688</v>
@@ -12043,7 +12043,7 @@
         <v>6</v>
       </c>
       <c r="J131" s="4">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K131" s="4" t="s">
         <v>693</v>
@@ -12081,7 +12081,7 @@
         <v>6</v>
       </c>
       <c r="J132" s="4">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K132" s="4" t="s">
         <v>698</v>
@@ -12119,7 +12119,7 @@
         <v>6</v>
       </c>
       <c r="J133" s="4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K133" s="4" t="s">
         <v>703</v>
@@ -12157,7 +12157,7 @@
         <v>6</v>
       </c>
       <c r="J134" s="4">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K134" s="4" t="s">
         <v>708</v>
@@ -12195,7 +12195,7 @@
         <v>6</v>
       </c>
       <c r="J135" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K135" s="4" t="s">
         <v>713</v>
@@ -12233,7 +12233,7 @@
         <v>6</v>
       </c>
       <c r="J136" s="4">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K136" s="4" t="s">
         <v>718</v>
@@ -12271,7 +12271,7 @@
         <v>6</v>
       </c>
       <c r="J137" s="4">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K137" s="4" t="s">
         <v>723</v>
@@ -12309,7 +12309,7 @@
         <v>6</v>
       </c>
       <c r="J138" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K138" s="4" t="s">
         <v>728</v>
@@ -12347,7 +12347,7 @@
         <v>6</v>
       </c>
       <c r="J139" s="4">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K139" s="4" t="s">
         <v>733</v>
@@ -12385,7 +12385,7 @@
         <v>6</v>
       </c>
       <c r="J140" s="4">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K140" s="4" t="s">
         <v>738</v>
@@ -12423,7 +12423,7 @@
         <v>6</v>
       </c>
       <c r="J141" s="4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K141" s="4" t="s">
         <v>743</v>
@@ -12461,7 +12461,7 @@
         <v>6</v>
       </c>
       <c r="J142" s="4">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="K142" s="4" t="s">
         <v>748</v>
@@ -12499,7 +12499,7 @@
         <v>6</v>
       </c>
       <c r="J143" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K143" s="4" t="s">
         <v>753</v>
@@ -12537,7 +12537,7 @@
         <v>6</v>
       </c>
       <c r="J144" s="4">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K144" s="4" t="s">
         <v>758</v>
@@ -12575,7 +12575,7 @@
         <v>6</v>
       </c>
       <c r="J145" s="4">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="K145" s="4" t="s">
         <v>763</v>
@@ -12613,7 +12613,7 @@
         <v>6</v>
       </c>
       <c r="J146" s="4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K146" s="4" t="s">
         <v>768</v>
@@ -12651,7 +12651,7 @@
         <v>6</v>
       </c>
       <c r="J147" s="4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K147" s="4" t="s">
         <v>773</v>
@@ -12689,7 +12689,7 @@
         <v>6</v>
       </c>
       <c r="J148" s="4">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="K148" s="4" t="s">
         <v>778</v>
@@ -12727,7 +12727,7 @@
         <v>6</v>
       </c>
       <c r="J149" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K149" s="4" t="s">
         <v>783</v>
@@ -12765,7 +12765,7 @@
         <v>6</v>
       </c>
       <c r="J150" s="4">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K150" s="4" t="s">
         <v>788</v>
@@ -12803,7 +12803,7 @@
         <v>6</v>
       </c>
       <c r="J151" s="4">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="K151" s="4" t="s">
         <v>793</v>
@@ -12841,7 +12841,7 @@
         <v>6</v>
       </c>
       <c r="J152" s="4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K152" s="4" t="s">
         <v>798</v>
@@ -12879,7 +12879,7 @@
         <v>6</v>
       </c>
       <c r="J153" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K153" s="4" t="s">
         <v>803</v>
@@ -12917,7 +12917,7 @@
         <v>6</v>
       </c>
       <c r="J154" s="4">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K154" s="4" t="s">
         <v>808</v>
@@ -12955,7 +12955,7 @@
         <v>6</v>
       </c>
       <c r="J155" s="4">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K155" s="4" t="s">
         <v>813</v>
@@ -12993,7 +12993,7 @@
         <v>6</v>
       </c>
       <c r="J156" s="4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K156" s="4" t="s">
         <v>818</v>
@@ -13031,7 +13031,7 @@
         <v>6</v>
       </c>
       <c r="J157" s="4">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K157" s="4" t="s">
         <v>823</v>
@@ -13069,7 +13069,7 @@
         <v>6</v>
       </c>
       <c r="J158" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K158" s="4" t="s">
         <v>828</v>
@@ -13107,7 +13107,7 @@
         <v>6</v>
       </c>
       <c r="J159" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K159" s="4" t="s">
         <v>833</v>
@@ -13145,7 +13145,7 @@
         <v>6</v>
       </c>
       <c r="J160" s="4">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K160" s="4" t="s">
         <v>838</v>
@@ -13183,7 +13183,7 @@
         <v>6</v>
       </c>
       <c r="J161" s="4">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K161" s="4" t="s">
         <v>843</v>
@@ -13221,7 +13221,7 @@
         <v>6</v>
       </c>
       <c r="J162" s="4">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K162" s="4" t="s">
         <v>848</v>
@@ -13297,7 +13297,7 @@
         <v>6</v>
       </c>
       <c r="J164" s="4">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="K164" s="4" t="s">
         <v>857</v>
@@ -13335,7 +13335,7 @@
         <v>6</v>
       </c>
       <c r="J165" s="4">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="K165" s="4" t="s">
         <v>861</v>
@@ -13373,7 +13373,7 @@
         <v>6</v>
       </c>
       <c r="J166" s="4">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K166" s="4" t="s">
         <v>866</v>
@@ -13411,7 +13411,7 @@
         <v>6</v>
       </c>
       <c r="J167" s="4">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K167" s="4" t="s">
         <v>871</v>
@@ -13449,7 +13449,7 @@
         <v>6</v>
       </c>
       <c r="J168" s="4">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K168" s="4" t="s">
         <v>876</v>
@@ -13487,7 +13487,7 @@
         <v>6</v>
       </c>
       <c r="J169" s="4">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K169" s="4" t="s">
         <v>881</v>
@@ -13525,7 +13525,7 @@
         <v>6</v>
       </c>
       <c r="J170" s="4">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="K170" s="4" t="s">
         <v>886</v>
@@ -13601,7 +13601,7 @@
         <v>6</v>
       </c>
       <c r="J172" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K172" s="4" t="s">
         <v>896</v>
@@ -13639,7 +13639,7 @@
         <v>6</v>
       </c>
       <c r="J173" s="4">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K173" s="4" t="s">
         <v>901</v>
@@ -13677,7 +13677,7 @@
         <v>6</v>
       </c>
       <c r="J174" s="4">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K174" s="4" t="s">
         <v>906</v>
@@ -13715,7 +13715,7 @@
         <v>6</v>
       </c>
       <c r="J175" s="4">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K175" s="4" t="s">
         <v>911</v>
@@ -13753,7 +13753,7 @@
         <v>6</v>
       </c>
       <c r="J176" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K176" s="4" t="s">
         <v>916</v>
@@ -13791,7 +13791,7 @@
         <v>6</v>
       </c>
       <c r="J177" s="4">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K177" s="4" t="s">
         <v>921</v>
@@ -13829,7 +13829,7 @@
         <v>6</v>
       </c>
       <c r="J178" s="4">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K178" s="4" t="s">
         <v>926</v>
@@ -13905,7 +13905,7 @@
         <v>6</v>
       </c>
       <c r="J180" s="4">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K180" s="4" t="s">
         <v>936</v>
@@ -13943,7 +13943,7 @@
         <v>6</v>
       </c>
       <c r="J181" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K181" s="4" t="s">
         <v>941</v>
@@ -13981,7 +13981,7 @@
         <v>6</v>
       </c>
       <c r="J182" s="4">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K182" s="4" t="s">
         <v>946</v>
